--- a/staticFiles/uploads/import.xlsx
+++ b/staticFiles/uploads/import.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giuseppe.manzella\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2524763-8847-4D54-B94C-4DC55521E06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BA7C7A5-AA27-46E4-A527-666A9374B9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8C146CD2-0BE0-42FA-9F2D-CA752C871441}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84D1F63F-B714-4CB6-9F75-142108F1EFD2}"/>
   </bookViews>
   <sheets>
-    <sheet name="3B - 1BIM" sheetId="1" r:id="rId1"/>
+    <sheet name="3B - 2BIM" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Causas1" localSheetId="0">'3B - 1BIM'!$B$23:$R$53</definedName>
+    <definedName name="Causas1" localSheetId="0">'3B - 2BIM'!$B$23:$R$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="37">
   <si>
     <r>
       <rPr>
@@ -47,6 +47,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>E.E. PROFª ALICE VILELA GALVÃO - ATA DO CONSELHO -</t>
     </r>
@@ -56,14 +57,16 @@
         <sz val="14"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 1º BIMESTRE 2024</t>
+      <t xml:space="preserve"> 2º BIMESTRE 2024</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -73,6 +76,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">PRINCIPAIS CAUSAS DE DIFICULDADE DOS ALUNOS - </t>
     </r>
@@ -82,6 +86,7 @@
         <sz val="14"/>
         <color rgb="FF1C4587"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>SÉRIE: 3B</t>
     </r>
@@ -532,7 +537,10 @@
     <t>REMANEJADO (A)</t>
   </si>
   <si>
-    <t>x</t>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>TRANSFERIDO (A)</t>
   </si>
   <si>
     <t>X</t>
@@ -541,19 +549,7 @@
     <t>OK</t>
   </si>
   <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>TRANSFERIDO (A)</t>
-  </si>
-  <si>
-    <t>FÍSICA/ FILO SOC. MOD</t>
-  </si>
-  <si>
-    <t>FÍSICA/TEC</t>
-  </si>
-  <si>
-    <t>FILO. SOC. MOD</t>
+    <t>REDAÇÃO</t>
   </si>
 </sst>
 </file>
@@ -565,51 +561,60 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF1C4587"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -626,18 +631,21 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -666,7 +674,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -937,9 +945,7 @@
       <top style="thin">
         <color rgb="FFFFF2CC"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -950,9 +956,7 @@
       <top style="thin">
         <color rgb="FFFFF2CC"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -993,6 +997,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFFF2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFF2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -1033,7 +1061,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1106,9 +1134,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1120,40 +1145,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1522,9 +1549,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A6C585-3743-402D-92D0-437888D7D2EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A39A2FB0-38FB-48EA-BE1B-87067D2ADF89}">
   <sheetPr>
-    <tabColor rgb="FF274E13"/>
+    <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2491,8 +2518,8 @@
       <c r="V23" s="39"/>
       <c r="W23" s="39"/>
       <c r="X23" s="39"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="41" t="s">
+      <c r="Y23" s="37"/>
+      <c r="Z23" s="40" t="s">
         <v>31</v>
       </c>
       <c r="AA23" s="5"/>
@@ -2508,49 +2535,75 @@
       <c r="A24" s="35">
         <v>2</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" s="39"/>
+      <c r="B24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="O24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" s="36" t="s">
+        <v>32</v>
+      </c>
       <c r="S24" s="37"/>
-      <c r="T24" s="38" t="s">
-        <v>33</v>
-      </c>
+      <c r="T24" s="38"/>
       <c r="U24" s="39"/>
       <c r="V24" s="39"/>
       <c r="W24" s="39"/>
       <c r="X24" s="39"/>
-      <c r="Y24" s="40"/>
-      <c r="Z24" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA24" s="43"/>
-      <c r="AB24" s="43"/>
-      <c r="AC24" s="43"/>
-      <c r="AD24" s="43"/>
-      <c r="AE24" s="43"/>
-      <c r="AF24" s="43"/>
-      <c r="AG24" s="43"/>
-      <c r="AH24" s="44"/>
+      <c r="Y24" s="37"/>
+      <c r="Z24" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA24" s="5"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="5"/>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="5"/>
+      <c r="AG24" s="5"/>
+      <c r="AH24" s="6"/>
     </row>
     <row r="25" spans="1:34" ht="14.25" customHeight="1">
       <c r="A25" s="35">
@@ -2613,8 +2666,8 @@
       <c r="V25" s="39"/>
       <c r="W25" s="39"/>
       <c r="X25" s="39"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="41" t="s">
+      <c r="Y25" s="37"/>
+      <c r="Z25" s="40" t="s">
         <v>31</v>
       </c>
       <c r="AA25" s="5"/>
@@ -2631,7 +2684,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -2650,78 +2703,80 @@
       <c r="Q26" s="39"/>
       <c r="R26" s="39"/>
       <c r="S26" s="37"/>
-      <c r="T26" s="38"/>
+      <c r="T26" s="38" t="s">
+        <v>34</v>
+      </c>
       <c r="U26" s="39"/>
       <c r="V26" s="39"/>
       <c r="W26" s="39"/>
       <c r="X26" s="39"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA26" s="43"/>
-      <c r="AB26" s="43"/>
-      <c r="AC26" s="43"/>
-      <c r="AD26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="44"/>
+      <c r="Y26" s="37"/>
+      <c r="Z26" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA26" s="42"/>
+      <c r="AB26" s="42"/>
+      <c r="AC26" s="42"/>
+      <c r="AD26" s="42"/>
+      <c r="AE26" s="42"/>
+      <c r="AF26" s="42"/>
+      <c r="AG26" s="42"/>
+      <c r="AH26" s="43"/>
     </row>
     <row r="27" spans="1:34" ht="14.25" customHeight="1">
       <c r="A27" s="35">
         <v>5</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R27" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S27" s="37"/>
       <c r="T27" s="38"/>
@@ -2729,9 +2784,9 @@
       <c r="V27" s="39"/>
       <c r="W27" s="39"/>
       <c r="X27" s="39"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="41" t="s">
-        <v>36</v>
+      <c r="Y27" s="37"/>
+      <c r="Z27" s="40" t="s">
+        <v>33</v>
       </c>
       <c r="AA27" s="5"/>
       <c r="AB27" s="5"/>
@@ -2747,27 +2802,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" s="39"/>
-      <c r="D28" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="D28" s="39"/>
       <c r="E28" s="39"/>
-      <c r="F28" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="F28" s="39"/>
       <c r="G28" s="39"/>
-      <c r="H28" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H28" s="39"/>
       <c r="I28" s="39"/>
       <c r="J28" s="39"/>
       <c r="K28" s="39"/>
       <c r="L28" s="39"/>
-      <c r="M28" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="M28" s="39"/>
       <c r="N28" s="39"/>
       <c r="O28" s="39"/>
       <c r="P28" s="39"/>
@@ -2775,24 +2822,24 @@
       <c r="R28" s="39"/>
       <c r="S28" s="37"/>
       <c r="T28" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U28" s="39"/>
       <c r="V28" s="39"/>
       <c r="W28" s="39"/>
       <c r="X28" s="39"/>
-      <c r="Y28" s="40"/>
-      <c r="Z28" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA28" s="43"/>
-      <c r="AB28" s="43"/>
-      <c r="AC28" s="43"/>
-      <c r="AD28" s="43"/>
-      <c r="AE28" s="43"/>
-      <c r="AF28" s="43"/>
-      <c r="AG28" s="43"/>
-      <c r="AH28" s="44"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA28" s="42"/>
+      <c r="AB28" s="42"/>
+      <c r="AC28" s="42"/>
+      <c r="AD28" s="42"/>
+      <c r="AE28" s="42"/>
+      <c r="AF28" s="42"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="43"/>
     </row>
     <row r="29" spans="1:34" ht="14.25" customHeight="1">
       <c r="A29" s="35">
@@ -2800,15 +2847,11 @@
       </c>
       <c r="B29" s="39"/>
       <c r="C29" s="39"/>
-      <c r="D29" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="39"/>
-      <c r="H29" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H29" s="39"/>
       <c r="I29" s="39"/>
       <c r="J29" s="39"/>
       <c r="K29" s="39"/>
@@ -2825,77 +2868,73 @@
       <c r="V29" s="39"/>
       <c r="W29" s="39"/>
       <c r="X29" s="39"/>
-      <c r="Y29" s="40"/>
-      <c r="Z29" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA29" s="43"/>
-      <c r="AB29" s="43"/>
-      <c r="AC29" s="43"/>
-      <c r="AD29" s="43"/>
-      <c r="AE29" s="43"/>
-      <c r="AF29" s="43"/>
-      <c r="AG29" s="43"/>
-      <c r="AH29" s="44"/>
+      <c r="Y29" s="37"/>
+      <c r="Z29" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA29" s="42"/>
+      <c r="AB29" s="42"/>
+      <c r="AC29" s="42"/>
+      <c r="AD29" s="42"/>
+      <c r="AE29" s="42"/>
+      <c r="AF29" s="42"/>
+      <c r="AG29" s="42"/>
+      <c r="AH29" s="43"/>
     </row>
     <row r="30" spans="1:34" ht="14.25" customHeight="1">
       <c r="A30" s="35">
         <v>8</v>
       </c>
-      <c r="B30" s="39"/>
+      <c r="B30" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E30" s="39"/>
-      <c r="F30" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="F30" s="39"/>
       <c r="G30" s="39"/>
-      <c r="H30" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H30" s="39"/>
       <c r="I30" s="39"/>
-      <c r="J30" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="J30" s="39"/>
       <c r="K30" s="39"/>
-      <c r="L30" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="M30" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
       <c r="N30" s="39"/>
       <c r="O30" s="39"/>
       <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
+      <c r="Q30" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="R30" s="39"/>
       <c r="S30" s="37"/>
-      <c r="T30" s="38"/>
+      <c r="T30" s="38" t="s">
+        <v>34</v>
+      </c>
       <c r="U30" s="39"/>
       <c r="V30" s="39"/>
       <c r="W30" s="39"/>
       <c r="X30" s="39"/>
-      <c r="Y30" s="40"/>
-      <c r="Z30" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA30" s="43"/>
-      <c r="AB30" s="43"/>
-      <c r="AC30" s="43"/>
-      <c r="AD30" s="43"/>
-      <c r="AE30" s="43"/>
-      <c r="AF30" s="43"/>
-      <c r="AG30" s="43"/>
-      <c r="AH30" s="44"/>
+      <c r="Y30" s="37"/>
+      <c r="Z30" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA30" s="42"/>
+      <c r="AB30" s="42"/>
+      <c r="AC30" s="42"/>
+      <c r="AD30" s="42"/>
+      <c r="AE30" s="42"/>
+      <c r="AF30" s="42"/>
+      <c r="AG30" s="42"/>
+      <c r="AH30" s="43"/>
     </row>
     <row r="31" spans="1:34" ht="14.25" customHeight="1">
       <c r="A31" s="35">
         <v>9</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -2915,79 +2954,79 @@
       <c r="R31" s="39"/>
       <c r="S31" s="37"/>
       <c r="T31" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U31" s="39"/>
       <c r="V31" s="39"/>
       <c r="W31" s="39"/>
       <c r="X31" s="39"/>
-      <c r="Y31" s="40"/>
-      <c r="Z31" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA31" s="43"/>
-      <c r="AB31" s="43"/>
-      <c r="AC31" s="43"/>
-      <c r="AD31" s="43"/>
-      <c r="AE31" s="43"/>
-      <c r="AF31" s="43"/>
-      <c r="AG31" s="43"/>
-      <c r="AH31" s="44"/>
+      <c r="Y31" s="37"/>
+      <c r="Z31" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA31" s="42"/>
+      <c r="AB31" s="42"/>
+      <c r="AC31" s="42"/>
+      <c r="AD31" s="42"/>
+      <c r="AE31" s="42"/>
+      <c r="AF31" s="42"/>
+      <c r="AG31" s="42"/>
+      <c r="AH31" s="43"/>
     </row>
     <row r="32" spans="1:34" ht="14.25" customHeight="1">
       <c r="A32" s="35">
         <v>10</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R32" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S32" s="37"/>
       <c r="T32" s="38"/>
@@ -2995,9 +3034,9 @@
       <c r="V32" s="39"/>
       <c r="W32" s="39"/>
       <c r="X32" s="39"/>
-      <c r="Y32" s="40"/>
-      <c r="Z32" s="41" t="s">
-        <v>36</v>
+      <c r="Y32" s="37"/>
+      <c r="Z32" s="40" t="s">
+        <v>33</v>
       </c>
       <c r="AA32" s="5"/>
       <c r="AB32" s="5"/>
@@ -3015,13 +3054,15 @@
       <c r="B33" s="39"/>
       <c r="C33" s="39"/>
       <c r="D33" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="39"/>
+        <v>34</v>
+      </c>
+      <c r="E33" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="F33" s="39"/>
       <c r="G33" s="39"/>
       <c r="H33" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I33" s="39"/>
       <c r="J33" s="39"/>
@@ -3039,73 +3080,73 @@
       <c r="V33" s="39"/>
       <c r="W33" s="39"/>
       <c r="X33" s="39"/>
-      <c r="Y33" s="40"/>
-      <c r="Z33" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA33" s="43"/>
-      <c r="AB33" s="43"/>
-      <c r="AC33" s="43"/>
-      <c r="AD33" s="43"/>
-      <c r="AE33" s="43"/>
-      <c r="AF33" s="43"/>
-      <c r="AG33" s="43"/>
-      <c r="AH33" s="44"/>
+      <c r="Y33" s="37"/>
+      <c r="Z33" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA33" s="42"/>
+      <c r="AB33" s="42"/>
+      <c r="AC33" s="42"/>
+      <c r="AD33" s="42"/>
+      <c r="AE33" s="42"/>
+      <c r="AF33" s="42"/>
+      <c r="AG33" s="42"/>
+      <c r="AH33" s="43"/>
     </row>
     <row r="34" spans="1:34" ht="14.25" customHeight="1">
       <c r="A34" s="35">
         <v>12</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R34" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S34" s="37"/>
       <c r="T34" s="38"/>
@@ -3113,9 +3154,9 @@
       <c r="V34" s="39"/>
       <c r="W34" s="39"/>
       <c r="X34" s="39"/>
-      <c r="Y34" s="40"/>
-      <c r="Z34" s="41" t="s">
-        <v>36</v>
+      <c r="Y34" s="37"/>
+      <c r="Z34" s="40" t="s">
+        <v>33</v>
       </c>
       <c r="AA34" s="5"/>
       <c r="AB34" s="5"/>
@@ -3133,14 +3174,12 @@
       <c r="B35" s="39"/>
       <c r="C35" s="39"/>
       <c r="D35" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E35" s="39"/>
       <c r="F35" s="39"/>
       <c r="G35" s="39"/>
-      <c r="H35" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H35" s="39"/>
       <c r="I35" s="39"/>
       <c r="J35" s="39"/>
       <c r="K35" s="39"/>
@@ -3157,18 +3196,18 @@
       <c r="V35" s="39"/>
       <c r="W35" s="39"/>
       <c r="X35" s="39"/>
-      <c r="Y35" s="40"/>
-      <c r="Z35" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA35" s="43"/>
-      <c r="AB35" s="43"/>
-      <c r="AC35" s="43"/>
-      <c r="AD35" s="43"/>
-      <c r="AE35" s="43"/>
-      <c r="AF35" s="43"/>
-      <c r="AG35" s="43"/>
-      <c r="AH35" s="44"/>
+      <c r="Y35" s="37"/>
+      <c r="Z35" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA35" s="42"/>
+      <c r="AB35" s="42"/>
+      <c r="AC35" s="42"/>
+      <c r="AD35" s="42"/>
+      <c r="AE35" s="42"/>
+      <c r="AF35" s="42"/>
+      <c r="AG35" s="42"/>
+      <c r="AH35" s="43"/>
     </row>
     <row r="36" spans="1:34" ht="14.25" customHeight="1">
       <c r="A36" s="35">
@@ -3177,14 +3216,12 @@
       <c r="B36" s="39"/>
       <c r="C36" s="39"/>
       <c r="D36" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
       <c r="G36" s="39"/>
-      <c r="H36" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H36" s="39"/>
       <c r="I36" s="39"/>
       <c r="J36" s="39"/>
       <c r="K36" s="39"/>
@@ -3201,18 +3238,18 @@
       <c r="V36" s="39"/>
       <c r="W36" s="39"/>
       <c r="X36" s="39"/>
-      <c r="Y36" s="40"/>
-      <c r="Z36" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA36" s="43"/>
-      <c r="AB36" s="43"/>
-      <c r="AC36" s="43"/>
-      <c r="AD36" s="43"/>
-      <c r="AE36" s="43"/>
-      <c r="AF36" s="43"/>
-      <c r="AG36" s="43"/>
-      <c r="AH36" s="44"/>
+      <c r="Y36" s="37"/>
+      <c r="Z36" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA36" s="42"/>
+      <c r="AB36" s="42"/>
+      <c r="AC36" s="42"/>
+      <c r="AD36" s="42"/>
+      <c r="AE36" s="42"/>
+      <c r="AF36" s="42"/>
+      <c r="AG36" s="42"/>
+      <c r="AH36" s="43"/>
     </row>
     <row r="37" spans="1:34" ht="14.25" customHeight="1">
       <c r="A37" s="35">
@@ -3221,27 +3258,25 @@
       <c r="B37" s="39"/>
       <c r="C37" s="39"/>
       <c r="D37" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" s="39"/>
+        <v>34</v>
+      </c>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="G37" s="39"/>
-      <c r="H37" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H37" s="39"/>
       <c r="I37" s="39"/>
       <c r="J37" s="39"/>
-      <c r="K37" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="K37" s="39"/>
       <c r="L37" s="39"/>
       <c r="M37" s="39"/>
       <c r="N37" s="39"/>
       <c r="O37" s="39"/>
       <c r="P37" s="39"/>
-      <c r="Q37" s="39"/>
+      <c r="Q37" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="R37" s="39"/>
       <c r="S37" s="37"/>
       <c r="T37" s="38"/>
@@ -3249,36 +3284,32 @@
       <c r="V37" s="39"/>
       <c r="W37" s="39"/>
       <c r="X37" s="39"/>
-      <c r="Y37" s="40"/>
-      <c r="Z37" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="43"/>
-      <c r="AE37" s="43"/>
-      <c r="AF37" s="43"/>
-      <c r="AG37" s="43"/>
-      <c r="AH37" s="44"/>
+      <c r="Y37" s="37"/>
+      <c r="Z37" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA37" s="42"/>
+      <c r="AB37" s="42"/>
+      <c r="AC37" s="42"/>
+      <c r="AD37" s="42"/>
+      <c r="AE37" s="42"/>
+      <c r="AF37" s="42"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="43"/>
     </row>
     <row r="38" spans="1:34" ht="14.25" customHeight="1">
       <c r="A38" s="35">
         <v>16</v>
       </c>
-      <c r="B38" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="B38" s="39"/>
       <c r="C38" s="39"/>
       <c r="D38" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E38" s="39"/>
       <c r="F38" s="39"/>
       <c r="G38" s="39"/>
-      <c r="H38" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H38" s="39"/>
       <c r="I38" s="39"/>
       <c r="J38" s="39"/>
       <c r="K38" s="39"/>
@@ -3295,66 +3326,78 @@
       <c r="V38" s="39"/>
       <c r="W38" s="39"/>
       <c r="X38" s="39"/>
-      <c r="Y38" s="40"/>
-      <c r="Z38" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA38" s="43"/>
-      <c r="AB38" s="43"/>
-      <c r="AC38" s="43"/>
-      <c r="AD38" s="43"/>
-      <c r="AE38" s="43"/>
-      <c r="AF38" s="43"/>
-      <c r="AG38" s="43"/>
-      <c r="AH38" s="44"/>
+      <c r="Y38" s="37"/>
+      <c r="Z38" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA38" s="42"/>
+      <c r="AB38" s="42"/>
+      <c r="AC38" s="42"/>
+      <c r="AD38" s="42"/>
+      <c r="AE38" s="42"/>
+      <c r="AF38" s="42"/>
+      <c r="AG38" s="42"/>
+      <c r="AH38" s="43"/>
     </row>
     <row r="39" spans="1:34" ht="14.25" customHeight="1">
       <c r="A39" s="35">
         <v>17</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
+      <c r="F39" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="G39" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="H39" s="39"/>
+        <v>34</v>
+      </c>
+      <c r="H39" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="I39" s="39"/>
       <c r="J39" s="39"/>
       <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
+      <c r="L39" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="M39" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="N39" s="39"/>
       <c r="O39" s="39"/>
       <c r="P39" s="39"/>
-      <c r="Q39" s="39"/>
+      <c r="Q39" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="R39" s="39"/>
       <c r="S39" s="37"/>
       <c r="T39" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U39" s="39"/>
       <c r="V39" s="39"/>
       <c r="W39" s="39"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="40"/>
-      <c r="Z39" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA39" s="43"/>
-      <c r="AB39" s="43"/>
-      <c r="AC39" s="43"/>
-      <c r="AD39" s="43"/>
-      <c r="AE39" s="43"/>
-      <c r="AF39" s="43"/>
-      <c r="AG39" s="43"/>
-      <c r="AH39" s="44"/>
+      <c r="X39" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y39" s="37"/>
+      <c r="Z39" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AE39" s="42"/>
+      <c r="AF39" s="42"/>
+      <c r="AG39" s="42"/>
+      <c r="AH39" s="43"/>
     </row>
     <row r="40" spans="1:34" ht="14.25" customHeight="1">
       <c r="A40" s="35">
@@ -3417,8 +3460,8 @@
       <c r="V40" s="39"/>
       <c r="W40" s="39"/>
       <c r="X40" s="39"/>
-      <c r="Y40" s="40"/>
-      <c r="Z40" s="41" t="s">
+      <c r="Y40" s="37"/>
+      <c r="Z40" s="40" t="s">
         <v>31</v>
       </c>
       <c r="AA40" s="5"/>
@@ -3435,106 +3478,94 @@
         <v>19</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="39" t="s">
-        <v>32</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C41" s="39"/>
       <c r="D41" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E41" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="39" t="s">
-        <v>32</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
       <c r="G41" s="39"/>
-      <c r="H41" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H41" s="39"/>
       <c r="I41" s="39"/>
       <c r="J41" s="39"/>
       <c r="K41" s="39"/>
       <c r="L41" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M41" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N41" s="39"/>
-      <c r="O41" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="O41" s="39"/>
       <c r="P41" s="39"/>
       <c r="Q41" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R41" s="39"/>
       <c r="S41" s="37"/>
       <c r="T41" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U41" s="39"/>
       <c r="V41" s="39"/>
       <c r="W41" s="39"/>
       <c r="X41" s="39"/>
-      <c r="Y41" s="40"/>
-      <c r="Z41" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA41" s="43"/>
-      <c r="AB41" s="43"/>
-      <c r="AC41" s="43"/>
-      <c r="AD41" s="43"/>
-      <c r="AE41" s="43"/>
-      <c r="AF41" s="43"/>
-      <c r="AG41" s="43"/>
-      <c r="AH41" s="44"/>
+      <c r="Y41" s="37"/>
+      <c r="Z41" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA41" s="42"/>
+      <c r="AB41" s="42"/>
+      <c r="AC41" s="42"/>
+      <c r="AD41" s="42"/>
+      <c r="AE41" s="42"/>
+      <c r="AF41" s="42"/>
+      <c r="AG41" s="42"/>
+      <c r="AH41" s="43"/>
     </row>
     <row r="42" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A42" s="46">
+      <c r="A42" s="35">
         <v>20</v>
       </c>
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="47"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="45"/>
+      <c r="O42" s="45"/>
+      <c r="P42" s="45"/>
+      <c r="Q42" s="45"/>
+      <c r="R42" s="45"/>
       <c r="S42" s="37"/>
       <c r="T42" s="38"/>
       <c r="U42" s="39"/>
       <c r="V42" s="39"/>
       <c r="W42" s="39"/>
       <c r="X42" s="39"/>
-      <c r="Y42" s="40"/>
-      <c r="Z42" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA42" s="43"/>
-      <c r="AB42" s="43"/>
-      <c r="AC42" s="43"/>
-      <c r="AD42" s="43"/>
-      <c r="AE42" s="43"/>
-      <c r="AF42" s="43"/>
-      <c r="AG42" s="43"/>
-      <c r="AH42" s="44"/>
+      <c r="Y42" s="37"/>
+      <c r="Z42" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA42" s="42"/>
+      <c r="AB42" s="42"/>
+      <c r="AC42" s="42"/>
+      <c r="AD42" s="42"/>
+      <c r="AE42" s="42"/>
+      <c r="AF42" s="42"/>
+      <c r="AG42" s="42"/>
+      <c r="AH42" s="43"/>
     </row>
     <row r="43" spans="1:34" ht="14.25" customHeight="1">
       <c r="A43" s="35">
@@ -3543,14 +3574,12 @@
       <c r="B43" s="39"/>
       <c r="C43" s="39"/>
       <c r="D43" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E43" s="39"/>
       <c r="F43" s="39"/>
       <c r="G43" s="39"/>
-      <c r="H43" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H43" s="39"/>
       <c r="I43" s="39"/>
       <c r="J43" s="39"/>
       <c r="K43" s="39"/>
@@ -3567,25 +3596,25 @@
       <c r="V43" s="39"/>
       <c r="W43" s="39"/>
       <c r="X43" s="39"/>
-      <c r="Y43" s="40"/>
-      <c r="Z43" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA43" s="43"/>
-      <c r="AB43" s="43"/>
-      <c r="AC43" s="43"/>
-      <c r="AD43" s="43"/>
-      <c r="AE43" s="43"/>
-      <c r="AF43" s="43"/>
-      <c r="AG43" s="43"/>
-      <c r="AH43" s="44"/>
+      <c r="Y43" s="37"/>
+      <c r="Z43" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA43" s="42"/>
+      <c r="AB43" s="42"/>
+      <c r="AC43" s="42"/>
+      <c r="AD43" s="42"/>
+      <c r="AE43" s="42"/>
+      <c r="AF43" s="42"/>
+      <c r="AG43" s="42"/>
+      <c r="AH43" s="43"/>
     </row>
     <row r="44" spans="1:34" ht="14.25" customHeight="1">
       <c r="A44" s="35">
         <v>22</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
@@ -3605,39 +3634,41 @@
       <c r="R44" s="39"/>
       <c r="S44" s="37"/>
       <c r="T44" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U44" s="39"/>
       <c r="V44" s="39"/>
       <c r="W44" s="39"/>
       <c r="X44" s="39"/>
-      <c r="Y44" s="40"/>
-      <c r="Z44" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA44" s="43"/>
-      <c r="AB44" s="43"/>
-      <c r="AC44" s="43"/>
-      <c r="AD44" s="43"/>
-      <c r="AE44" s="43"/>
-      <c r="AF44" s="43"/>
-      <c r="AG44" s="43"/>
-      <c r="AH44" s="44"/>
+      <c r="Y44" s="37"/>
+      <c r="Z44" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA44" s="42"/>
+      <c r="AB44" s="42"/>
+      <c r="AC44" s="42"/>
+      <c r="AD44" s="42"/>
+      <c r="AE44" s="42"/>
+      <c r="AF44" s="42"/>
+      <c r="AG44" s="42"/>
+      <c r="AH44" s="43"/>
     </row>
     <row r="45" spans="1:34" ht="14.25" customHeight="1">
       <c r="A45" s="35">
         <v>23</v>
       </c>
-      <c r="B45" s="39"/>
+      <c r="B45" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="C45" s="39"/>
       <c r="D45" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E45" s="39"/>
       <c r="F45" s="39"/>
       <c r="G45" s="39"/>
       <c r="H45" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I45" s="39"/>
       <c r="J45" s="39"/>
@@ -3647,43 +3678,47 @@
       <c r="N45" s="39"/>
       <c r="O45" s="39"/>
       <c r="P45" s="39"/>
-      <c r="Q45" s="39"/>
+      <c r="Q45" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="R45" s="39"/>
       <c r="S45" s="37"/>
-      <c r="T45" s="38"/>
+      <c r="T45" s="38" t="s">
+        <v>34</v>
+      </c>
       <c r="U45" s="39"/>
       <c r="V45" s="39"/>
       <c r="W45" s="39"/>
       <c r="X45" s="39"/>
-      <c r="Y45" s="40"/>
-      <c r="Z45" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA45" s="43"/>
-      <c r="AB45" s="43"/>
-      <c r="AC45" s="43"/>
-      <c r="AD45" s="43"/>
-      <c r="AE45" s="43"/>
-      <c r="AF45" s="43"/>
-      <c r="AG45" s="43"/>
-      <c r="AH45" s="44"/>
+      <c r="Y45" s="37"/>
+      <c r="Z45" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA45" s="42"/>
+      <c r="AB45" s="42"/>
+      <c r="AC45" s="42"/>
+      <c r="AD45" s="42"/>
+      <c r="AE45" s="42"/>
+      <c r="AF45" s="42"/>
+      <c r="AG45" s="42"/>
+      <c r="AH45" s="43"/>
     </row>
     <row r="46" spans="1:34" ht="14.25" customHeight="1">
       <c r="A46" s="35">
         <v>24</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" s="39"/>
       <c r="D46" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E46" s="39"/>
       <c r="F46" s="39"/>
       <c r="G46" s="39"/>
       <c r="H46" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I46" s="39"/>
       <c r="J46" s="39"/>
@@ -3693,7 +3728,9 @@
       <c r="N46" s="39"/>
       <c r="O46" s="39"/>
       <c r="P46" s="39"/>
-      <c r="Q46" s="39"/>
+      <c r="Q46" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="R46" s="39"/>
       <c r="S46" s="37"/>
       <c r="T46" s="38"/>
@@ -3701,18 +3738,18 @@
       <c r="V46" s="39"/>
       <c r="W46" s="39"/>
       <c r="X46" s="39"/>
-      <c r="Y46" s="40"/>
-      <c r="Z46" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA46" s="43"/>
-      <c r="AB46" s="43"/>
-      <c r="AC46" s="43"/>
-      <c r="AD46" s="43"/>
-      <c r="AE46" s="43"/>
-      <c r="AF46" s="43"/>
-      <c r="AG46" s="43"/>
-      <c r="AH46" s="44"/>
+      <c r="Y46" s="37"/>
+      <c r="Z46" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA46" s="42"/>
+      <c r="AB46" s="42"/>
+      <c r="AC46" s="42"/>
+      <c r="AD46" s="42"/>
+      <c r="AE46" s="42"/>
+      <c r="AF46" s="42"/>
+      <c r="AG46" s="42"/>
+      <c r="AH46" s="43"/>
     </row>
     <row r="47" spans="1:34" ht="14.25" customHeight="1">
       <c r="A47" s="35">
@@ -3741,18 +3778,18 @@
       <c r="V47" s="39"/>
       <c r="W47" s="39"/>
       <c r="X47" s="39"/>
-      <c r="Y47" s="40"/>
-      <c r="Z47" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA47" s="43"/>
-      <c r="AB47" s="43"/>
-      <c r="AC47" s="43"/>
-      <c r="AD47" s="43"/>
-      <c r="AE47" s="43"/>
-      <c r="AF47" s="43"/>
-      <c r="AG47" s="43"/>
-      <c r="AH47" s="44"/>
+      <c r="Y47" s="37"/>
+      <c r="Z47" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA47" s="42"/>
+      <c r="AB47" s="42"/>
+      <c r="AC47" s="42"/>
+      <c r="AD47" s="42"/>
+      <c r="AE47" s="42"/>
+      <c r="AF47" s="42"/>
+      <c r="AG47" s="42"/>
+      <c r="AH47" s="43"/>
     </row>
     <row r="48" spans="1:34" ht="14.25" customHeight="1">
       <c r="A48" s="35">
@@ -3815,8 +3852,8 @@
       <c r="V48" s="39"/>
       <c r="W48" s="39"/>
       <c r="X48" s="39"/>
-      <c r="Y48" s="40"/>
-      <c r="Z48" s="41" t="s">
+      <c r="Y48" s="37"/>
+      <c r="Z48" s="40" t="s">
         <v>31</v>
       </c>
       <c r="AA48" s="5"/>
@@ -3833,46 +3870,48 @@
         <v>27</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49" s="39"/>
       <c r="D49" s="39"/>
       <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
+      <c r="F49" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="G49" s="39"/>
       <c r="H49" s="39"/>
       <c r="I49" s="39"/>
       <c r="J49" s="39"/>
-      <c r="K49" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="K49" s="39"/>
       <c r="L49" s="39"/>
       <c r="M49" s="39"/>
       <c r="N49" s="39"/>
       <c r="O49" s="39"/>
       <c r="P49" s="39"/>
-      <c r="Q49" s="39"/>
+      <c r="Q49" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="R49" s="39"/>
       <c r="S49" s="37"/>
       <c r="T49" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U49" s="39"/>
       <c r="V49" s="39"/>
       <c r="W49" s="39"/>
       <c r="X49" s="39"/>
-      <c r="Y49" s="40"/>
-      <c r="Z49" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA49" s="43"/>
-      <c r="AB49" s="43"/>
-      <c r="AC49" s="43"/>
-      <c r="AD49" s="43"/>
-      <c r="AE49" s="43"/>
-      <c r="AF49" s="43"/>
-      <c r="AG49" s="43"/>
-      <c r="AH49" s="44"/>
+      <c r="Y49" s="37"/>
+      <c r="Z49" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA49" s="42"/>
+      <c r="AB49" s="42"/>
+      <c r="AC49" s="42"/>
+      <c r="AD49" s="42"/>
+      <c r="AE49" s="42"/>
+      <c r="AF49" s="42"/>
+      <c r="AG49" s="42"/>
+      <c r="AH49" s="43"/>
     </row>
     <row r="50" spans="1:34" ht="14.25" customHeight="1">
       <c r="A50" s="35">
@@ -3880,7 +3919,9 @@
       </c>
       <c r="B50" s="39"/>
       <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
+      <c r="D50" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="E50" s="39"/>
       <c r="F50" s="39"/>
       <c r="G50" s="39"/>
@@ -3901,9 +3942,9 @@
       <c r="V50" s="39"/>
       <c r="W50" s="39"/>
       <c r="X50" s="39"/>
-      <c r="Y50" s="40"/>
-      <c r="Z50" s="48" t="s">
-        <v>34</v>
+      <c r="Y50" s="46"/>
+      <c r="Z50" s="47" t="s">
+        <v>35</v>
       </c>
       <c r="AA50" s="5"/>
       <c r="AB50" s="5"/>
@@ -3919,20 +3960,18 @@
         <v>29</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="39" t="s">
-        <v>32</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C51" s="39"/>
       <c r="D51" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
+      <c r="F51" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="G51" s="39"/>
-      <c r="H51" s="39" t="s">
-        <v>32</v>
-      </c>
+      <c r="H51" s="39"/>
       <c r="I51" s="39"/>
       <c r="J51" s="39"/>
       <c r="K51" s="39"/>
@@ -3941,19 +3980,19 @@
       <c r="N51" s="39"/>
       <c r="O51" s="39"/>
       <c r="P51" s="39"/>
-      <c r="Q51" s="39"/>
+      <c r="Q51" s="39" t="s">
+        <v>34</v>
+      </c>
       <c r="R51" s="39"/>
       <c r="S51" s="37"/>
-      <c r="T51" s="38" t="s">
-        <v>33</v>
-      </c>
+      <c r="T51" s="38"/>
       <c r="U51" s="39"/>
       <c r="V51" s="39"/>
       <c r="W51" s="39"/>
       <c r="X51" s="39"/>
-      <c r="Y51" s="40"/>
-      <c r="Z51" s="48" t="s">
-        <v>34</v>
+      <c r="Y51" s="46"/>
+      <c r="Z51" s="47" t="s">
+        <v>35</v>
       </c>
       <c r="AA51" s="5"/>
       <c r="AB51" s="5"/>
@@ -3968,31 +4007,67 @@
       <c r="A52" s="35">
         <v>30</v>
       </c>
-      <c r="B52" s="39"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="39"/>
-      <c r="O52" s="39"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="39"/>
+      <c r="B52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="K52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="O52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="P52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="R52" s="36" t="s">
+        <v>32</v>
+      </c>
       <c r="S52" s="37"/>
       <c r="T52" s="38"/>
       <c r="U52" s="39"/>
       <c r="V52" s="39"/>
       <c r="W52" s="39"/>
       <c r="X52" s="39"/>
-      <c r="Y52" s="40"/>
-      <c r="Z52" s="48"/>
+      <c r="Y52" s="46"/>
+      <c r="Z52" s="40" t="s">
+        <v>33</v>
+      </c>
       <c r="AA52" s="5"/>
       <c r="AB52" s="5"/>
       <c r="AC52" s="5"/>
@@ -4029,8 +4104,10 @@
       <c r="V53" s="39"/>
       <c r="W53" s="39"/>
       <c r="X53" s="39"/>
-      <c r="Y53" s="40"/>
-      <c r="Z53" s="49"/>
+      <c r="Y53" s="46"/>
+      <c r="Z53" s="47" t="s">
+        <v>35</v>
+      </c>
       <c r="AA53" s="5"/>
       <c r="AB53" s="5"/>
       <c r="AC53" s="5"/>
@@ -4154,17 +4231,17 @@
         <v>5</v>
       </c>
       <c r="Y55" s="31"/>
-      <c r="Z55" s="32" t="s">
+      <c r="Z55" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="AA55" s="33"/>
-      <c r="AB55" s="33"/>
-      <c r="AC55" s="33"/>
-      <c r="AD55" s="33"/>
-      <c r="AE55" s="33"/>
-      <c r="AF55" s="33"/>
-      <c r="AG55" s="33"/>
-      <c r="AH55" s="34"/>
+      <c r="AA55" s="49"/>
+      <c r="AB55" s="49"/>
+      <c r="AC55" s="49"/>
+      <c r="AD55" s="49"/>
+      <c r="AE55" s="49"/>
+      <c r="AF55" s="49"/>
+      <c r="AG55" s="49"/>
+      <c r="AH55" s="50"/>
     </row>
     <row r="56" spans="1:34" ht="14.25" customHeight="1">
       <c r="A56" s="35">
@@ -4194,16 +4271,16 @@
       <c r="V56" s="39"/>
       <c r="W56" s="39"/>
       <c r="X56" s="39"/>
-      <c r="Y56" s="40"/>
-      <c r="Z56" s="50"/>
-      <c r="AA56" s="43"/>
-      <c r="AB56" s="43"/>
-      <c r="AC56" s="43"/>
-      <c r="AD56" s="43"/>
-      <c r="AE56" s="43"/>
-      <c r="AF56" s="43"/>
-      <c r="AG56" s="43"/>
-      <c r="AH56" s="44"/>
+      <c r="Y56" s="46"/>
+      <c r="Z56" s="51"/>
+      <c r="AA56" s="42"/>
+      <c r="AB56" s="42"/>
+      <c r="AC56" s="42"/>
+      <c r="AD56" s="42"/>
+      <c r="AE56" s="42"/>
+      <c r="AF56" s="42"/>
+      <c r="AG56" s="42"/>
+      <c r="AH56" s="43"/>
     </row>
     <row r="57" spans="1:34" ht="14.25" customHeight="1">
       <c r="A57" s="35">
@@ -4233,16 +4310,16 @@
       <c r="V57" s="39"/>
       <c r="W57" s="39"/>
       <c r="X57" s="39"/>
-      <c r="Y57" s="40"/>
-      <c r="Z57" s="50"/>
-      <c r="AA57" s="43"/>
-      <c r="AB57" s="43"/>
-      <c r="AC57" s="43"/>
-      <c r="AD57" s="43"/>
-      <c r="AE57" s="43"/>
-      <c r="AF57" s="43"/>
-      <c r="AG57" s="43"/>
-      <c r="AH57" s="44"/>
+      <c r="Y57" s="46"/>
+      <c r="Z57" s="51"/>
+      <c r="AA57" s="42"/>
+      <c r="AB57" s="42"/>
+      <c r="AC57" s="42"/>
+      <c r="AD57" s="42"/>
+      <c r="AE57" s="42"/>
+      <c r="AF57" s="42"/>
+      <c r="AG57" s="42"/>
+      <c r="AH57" s="43"/>
     </row>
     <row r="58" spans="1:34" ht="14.25" customHeight="1">
       <c r="A58" s="35">
@@ -4272,16 +4349,16 @@
       <c r="V58" s="39"/>
       <c r="W58" s="39"/>
       <c r="X58" s="39"/>
-      <c r="Y58" s="40"/>
-      <c r="Z58" s="50"/>
-      <c r="AA58" s="43"/>
-      <c r="AB58" s="43"/>
-      <c r="AC58" s="43"/>
-      <c r="AD58" s="43"/>
-      <c r="AE58" s="43"/>
-      <c r="AF58" s="43"/>
-      <c r="AG58" s="43"/>
-      <c r="AH58" s="44"/>
+      <c r="Y58" s="46"/>
+      <c r="Z58" s="51"/>
+      <c r="AA58" s="42"/>
+      <c r="AB58" s="42"/>
+      <c r="AC58" s="42"/>
+      <c r="AD58" s="42"/>
+      <c r="AE58" s="42"/>
+      <c r="AF58" s="42"/>
+      <c r="AG58" s="42"/>
+      <c r="AH58" s="43"/>
     </row>
     <row r="59" spans="1:34" ht="14.25" customHeight="1">
       <c r="A59" s="35">
@@ -4311,16 +4388,16 @@
       <c r="V59" s="39"/>
       <c r="W59" s="39"/>
       <c r="X59" s="39"/>
-      <c r="Y59" s="40"/>
-      <c r="Z59" s="50"/>
-      <c r="AA59" s="43"/>
-      <c r="AB59" s="43"/>
-      <c r="AC59" s="43"/>
-      <c r="AD59" s="43"/>
-      <c r="AE59" s="43"/>
-      <c r="AF59" s="43"/>
-      <c r="AG59" s="43"/>
-      <c r="AH59" s="44"/>
+      <c r="Y59" s="46"/>
+      <c r="Z59" s="51"/>
+      <c r="AA59" s="42"/>
+      <c r="AB59" s="42"/>
+      <c r="AC59" s="42"/>
+      <c r="AD59" s="42"/>
+      <c r="AE59" s="42"/>
+      <c r="AF59" s="42"/>
+      <c r="AG59" s="42"/>
+      <c r="AH59" s="43"/>
     </row>
     <row r="60" spans="1:34" ht="14.25" customHeight="1">
       <c r="A60" s="35">
@@ -4350,16 +4427,16 @@
       <c r="V60" s="39"/>
       <c r="W60" s="39"/>
       <c r="X60" s="39"/>
-      <c r="Y60" s="40"/>
-      <c r="Z60" s="50"/>
-      <c r="AA60" s="43"/>
-      <c r="AB60" s="43"/>
-      <c r="AC60" s="43"/>
-      <c r="AD60" s="43"/>
-      <c r="AE60" s="43"/>
-      <c r="AF60" s="43"/>
-      <c r="AG60" s="43"/>
-      <c r="AH60" s="44"/>
+      <c r="Y60" s="46"/>
+      <c r="Z60" s="51"/>
+      <c r="AA60" s="42"/>
+      <c r="AB60" s="42"/>
+      <c r="AC60" s="42"/>
+      <c r="AD60" s="42"/>
+      <c r="AE60" s="42"/>
+      <c r="AF60" s="42"/>
+      <c r="AG60" s="42"/>
+      <c r="AH60" s="43"/>
     </row>
     <row r="61" spans="1:34" ht="14.25" customHeight="1">
       <c r="A61" s="35">
@@ -4389,16 +4466,16 @@
       <c r="V61" s="39"/>
       <c r="W61" s="39"/>
       <c r="X61" s="39"/>
-      <c r="Y61" s="40"/>
-      <c r="Z61" s="50"/>
-      <c r="AA61" s="43"/>
-      <c r="AB61" s="43"/>
-      <c r="AC61" s="43"/>
-      <c r="AD61" s="43"/>
-      <c r="AE61" s="43"/>
-      <c r="AF61" s="43"/>
-      <c r="AG61" s="43"/>
-      <c r="AH61" s="44"/>
+      <c r="Y61" s="46"/>
+      <c r="Z61" s="51"/>
+      <c r="AA61" s="42"/>
+      <c r="AB61" s="42"/>
+      <c r="AC61" s="42"/>
+      <c r="AD61" s="42"/>
+      <c r="AE61" s="42"/>
+      <c r="AF61" s="42"/>
+      <c r="AG61" s="42"/>
+      <c r="AH61" s="43"/>
     </row>
     <row r="62" spans="1:34" ht="14.25" customHeight="1">
       <c r="A62" s="35">
@@ -4428,16 +4505,16 @@
       <c r="V62" s="39"/>
       <c r="W62" s="39"/>
       <c r="X62" s="39"/>
-      <c r="Y62" s="40"/>
-      <c r="Z62" s="50"/>
-      <c r="AA62" s="43"/>
-      <c r="AB62" s="43"/>
-      <c r="AC62" s="43"/>
-      <c r="AD62" s="43"/>
-      <c r="AE62" s="43"/>
-      <c r="AF62" s="43"/>
-      <c r="AG62" s="43"/>
-      <c r="AH62" s="44"/>
+      <c r="Y62" s="46"/>
+      <c r="Z62" s="51"/>
+      <c r="AA62" s="42"/>
+      <c r="AB62" s="42"/>
+      <c r="AC62" s="42"/>
+      <c r="AD62" s="42"/>
+      <c r="AE62" s="42"/>
+      <c r="AF62" s="42"/>
+      <c r="AG62" s="42"/>
+      <c r="AH62" s="43"/>
     </row>
     <row r="63" spans="1:34" ht="14.25" customHeight="1">
       <c r="A63" s="35">
@@ -4467,16 +4544,16 @@
       <c r="V63" s="39"/>
       <c r="W63" s="39"/>
       <c r="X63" s="39"/>
-      <c r="Y63" s="40"/>
-      <c r="Z63" s="50"/>
-      <c r="AA63" s="43"/>
-      <c r="AB63" s="43"/>
-      <c r="AC63" s="43"/>
-      <c r="AD63" s="43"/>
-      <c r="AE63" s="43"/>
-      <c r="AF63" s="43"/>
-      <c r="AG63" s="43"/>
-      <c r="AH63" s="44"/>
+      <c r="Y63" s="46"/>
+      <c r="Z63" s="51"/>
+      <c r="AA63" s="42"/>
+      <c r="AB63" s="42"/>
+      <c r="AC63" s="42"/>
+      <c r="AD63" s="42"/>
+      <c r="AE63" s="42"/>
+      <c r="AF63" s="42"/>
+      <c r="AG63" s="42"/>
+      <c r="AH63" s="43"/>
     </row>
     <row r="64" spans="1:34" ht="14.25" customHeight="1">
       <c r="A64" s="35">
@@ -4506,16 +4583,16 @@
       <c r="V64" s="39"/>
       <c r="W64" s="39"/>
       <c r="X64" s="39"/>
-      <c r="Y64" s="40"/>
-      <c r="Z64" s="50"/>
-      <c r="AA64" s="43"/>
-      <c r="AB64" s="43"/>
-      <c r="AC64" s="43"/>
-      <c r="AD64" s="43"/>
-      <c r="AE64" s="43"/>
-      <c r="AF64" s="43"/>
-      <c r="AG64" s="43"/>
-      <c r="AH64" s="44"/>
+      <c r="Y64" s="46"/>
+      <c r="Z64" s="51"/>
+      <c r="AA64" s="42"/>
+      <c r="AB64" s="42"/>
+      <c r="AC64" s="42"/>
+      <c r="AD64" s="42"/>
+      <c r="AE64" s="42"/>
+      <c r="AF64" s="42"/>
+      <c r="AG64" s="42"/>
+      <c r="AH64" s="43"/>
     </row>
     <row r="65" spans="1:34" ht="14.25" customHeight="1">
       <c r="A65" s="35">
@@ -4545,16 +4622,16 @@
       <c r="V65" s="39"/>
       <c r="W65" s="39"/>
       <c r="X65" s="39"/>
-      <c r="Y65" s="40"/>
-      <c r="Z65" s="50"/>
-      <c r="AA65" s="43"/>
-      <c r="AB65" s="43"/>
-      <c r="AC65" s="43"/>
-      <c r="AD65" s="43"/>
-      <c r="AE65" s="43"/>
-      <c r="AF65" s="43"/>
-      <c r="AG65" s="43"/>
-      <c r="AH65" s="44"/>
+      <c r="Y65" s="46"/>
+      <c r="Z65" s="51"/>
+      <c r="AA65" s="42"/>
+      <c r="AB65" s="42"/>
+      <c r="AC65" s="42"/>
+      <c r="AD65" s="42"/>
+      <c r="AE65" s="42"/>
+      <c r="AF65" s="42"/>
+      <c r="AG65" s="42"/>
+      <c r="AH65" s="43"/>
     </row>
     <row r="66" spans="1:34" ht="14.25" customHeight="1">
       <c r="A66" s="35">
@@ -4584,16 +4661,16 @@
       <c r="V66" s="39"/>
       <c r="W66" s="39"/>
       <c r="X66" s="39"/>
-      <c r="Y66" s="40"/>
-      <c r="Z66" s="50"/>
-      <c r="AA66" s="43"/>
-      <c r="AB66" s="43"/>
-      <c r="AC66" s="43"/>
-      <c r="AD66" s="43"/>
-      <c r="AE66" s="43"/>
-      <c r="AF66" s="43"/>
-      <c r="AG66" s="43"/>
-      <c r="AH66" s="44"/>
+      <c r="Y66" s="46"/>
+      <c r="Z66" s="51"/>
+      <c r="AA66" s="42"/>
+      <c r="AB66" s="42"/>
+      <c r="AC66" s="42"/>
+      <c r="AD66" s="42"/>
+      <c r="AE66" s="42"/>
+      <c r="AF66" s="42"/>
+      <c r="AG66" s="42"/>
+      <c r="AH66" s="43"/>
     </row>
     <row r="67" spans="1:34" ht="14.25" customHeight="1">
       <c r="A67" s="35">
@@ -4623,16 +4700,16 @@
       <c r="V67" s="39"/>
       <c r="W67" s="39"/>
       <c r="X67" s="39"/>
-      <c r="Y67" s="40"/>
-      <c r="Z67" s="50"/>
-      <c r="AA67" s="43"/>
-      <c r="AB67" s="43"/>
-      <c r="AC67" s="43"/>
-      <c r="AD67" s="43"/>
-      <c r="AE67" s="43"/>
-      <c r="AF67" s="43"/>
-      <c r="AG67" s="43"/>
-      <c r="AH67" s="44"/>
+      <c r="Y67" s="46"/>
+      <c r="Z67" s="51"/>
+      <c r="AA67" s="42"/>
+      <c r="AB67" s="42"/>
+      <c r="AC67" s="42"/>
+      <c r="AD67" s="42"/>
+      <c r="AE67" s="42"/>
+      <c r="AF67" s="42"/>
+      <c r="AG67" s="42"/>
+      <c r="AH67" s="43"/>
     </row>
     <row r="68" spans="1:34" ht="14.25" customHeight="1">
       <c r="A68" s="35">
@@ -4662,16 +4739,16 @@
       <c r="V68" s="39"/>
       <c r="W68" s="39"/>
       <c r="X68" s="39"/>
-      <c r="Y68" s="40"/>
-      <c r="Z68" s="51"/>
-      <c r="AA68" s="43"/>
-      <c r="AB68" s="43"/>
-      <c r="AC68" s="43"/>
-      <c r="AD68" s="43"/>
-      <c r="AE68" s="43"/>
-      <c r="AF68" s="43"/>
-      <c r="AG68" s="43"/>
-      <c r="AH68" s="44"/>
+      <c r="Y68" s="46"/>
+      <c r="Z68" s="52"/>
+      <c r="AA68" s="42"/>
+      <c r="AB68" s="42"/>
+      <c r="AC68" s="42"/>
+      <c r="AD68" s="42"/>
+      <c r="AE68" s="42"/>
+      <c r="AF68" s="42"/>
+      <c r="AG68" s="42"/>
+      <c r="AH68" s="43"/>
     </row>
     <row r="69" spans="1:34" ht="14.25" customHeight="1">
       <c r="A69" s="35">
@@ -4701,16 +4778,16 @@
       <c r="V69" s="39"/>
       <c r="W69" s="39"/>
       <c r="X69" s="39"/>
-      <c r="Y69" s="40"/>
-      <c r="Z69" s="51"/>
-      <c r="AA69" s="43"/>
-      <c r="AB69" s="43"/>
-      <c r="AC69" s="43"/>
-      <c r="AD69" s="43"/>
-      <c r="AE69" s="43"/>
-      <c r="AF69" s="43"/>
-      <c r="AG69" s="43"/>
-      <c r="AH69" s="44"/>
+      <c r="Y69" s="46"/>
+      <c r="Z69" s="52"/>
+      <c r="AA69" s="42"/>
+      <c r="AB69" s="42"/>
+      <c r="AC69" s="42"/>
+      <c r="AD69" s="42"/>
+      <c r="AE69" s="42"/>
+      <c r="AF69" s="42"/>
+      <c r="AG69" s="42"/>
+      <c r="AH69" s="43"/>
     </row>
     <row r="70" spans="1:34" ht="14.25" customHeight="1">
       <c r="A70" s="35">
@@ -4740,16 +4817,16 @@
       <c r="V70" s="39"/>
       <c r="W70" s="39"/>
       <c r="X70" s="39"/>
-      <c r="Y70" s="40"/>
-      <c r="Z70" s="51"/>
-      <c r="AA70" s="43"/>
-      <c r="AB70" s="43"/>
-      <c r="AC70" s="43"/>
-      <c r="AD70" s="43"/>
-      <c r="AE70" s="43"/>
-      <c r="AF70" s="43"/>
-      <c r="AG70" s="43"/>
-      <c r="AH70" s="44"/>
+      <c r="Y70" s="46"/>
+      <c r="Z70" s="52"/>
+      <c r="AA70" s="42"/>
+      <c r="AB70" s="42"/>
+      <c r="AC70" s="42"/>
+      <c r="AD70" s="42"/>
+      <c r="AE70" s="42"/>
+      <c r="AF70" s="42"/>
+      <c r="AG70" s="42"/>
+      <c r="AH70" s="43"/>
     </row>
     <row r="71" spans="1:34" ht="14.25" customHeight="1">
       <c r="A71" s="35">
@@ -4779,16 +4856,16 @@
       <c r="V71" s="39"/>
       <c r="W71" s="39"/>
       <c r="X71" s="39"/>
-      <c r="Y71" s="40"/>
-      <c r="Z71" s="51"/>
-      <c r="AA71" s="43"/>
-      <c r="AB71" s="43"/>
-      <c r="AC71" s="43"/>
-      <c r="AD71" s="43"/>
-      <c r="AE71" s="43"/>
-      <c r="AF71" s="43"/>
-      <c r="AG71" s="43"/>
-      <c r="AH71" s="44"/>
+      <c r="Y71" s="46"/>
+      <c r="Z71" s="52"/>
+      <c r="AA71" s="42"/>
+      <c r="AB71" s="42"/>
+      <c r="AC71" s="42"/>
+      <c r="AD71" s="42"/>
+      <c r="AE71" s="42"/>
+      <c r="AF71" s="42"/>
+      <c r="AG71" s="42"/>
+      <c r="AH71" s="43"/>
     </row>
     <row r="72" spans="1:34" ht="14.25" customHeight="1">
       <c r="A72" s="35">
@@ -4818,16 +4895,16 @@
       <c r="V72" s="39"/>
       <c r="W72" s="39"/>
       <c r="X72" s="39"/>
-      <c r="Y72" s="40"/>
-      <c r="Z72" s="51"/>
-      <c r="AA72" s="43"/>
-      <c r="AB72" s="43"/>
-      <c r="AC72" s="43"/>
-      <c r="AD72" s="43"/>
-      <c r="AE72" s="43"/>
-      <c r="AF72" s="43"/>
-      <c r="AG72" s="43"/>
-      <c r="AH72" s="44"/>
+      <c r="Y72" s="46"/>
+      <c r="Z72" s="52"/>
+      <c r="AA72" s="42"/>
+      <c r="AB72" s="42"/>
+      <c r="AC72" s="42"/>
+      <c r="AD72" s="42"/>
+      <c r="AE72" s="42"/>
+      <c r="AF72" s="42"/>
+      <c r="AG72" s="42"/>
+      <c r="AH72" s="43"/>
     </row>
     <row r="73" spans="1:34" ht="14.25" customHeight="1">
       <c r="A73" s="35">
@@ -4857,16 +4934,16 @@
       <c r="V73" s="39"/>
       <c r="W73" s="39"/>
       <c r="X73" s="39"/>
-      <c r="Y73" s="40"/>
-      <c r="Z73" s="51"/>
-      <c r="AA73" s="43"/>
-      <c r="AB73" s="43"/>
-      <c r="AC73" s="43"/>
-      <c r="AD73" s="43"/>
-      <c r="AE73" s="43"/>
-      <c r="AF73" s="43"/>
-      <c r="AG73" s="43"/>
-      <c r="AH73" s="44"/>
+      <c r="Y73" s="46"/>
+      <c r="Z73" s="52"/>
+      <c r="AA73" s="42"/>
+      <c r="AB73" s="42"/>
+      <c r="AC73" s="42"/>
+      <c r="AD73" s="42"/>
+      <c r="AE73" s="42"/>
+      <c r="AF73" s="42"/>
+      <c r="AG73" s="42"/>
+      <c r="AH73" s="43"/>
     </row>
     <row r="74" spans="1:34" ht="14.25" customHeight="1">
       <c r="A74" s="35">
@@ -4896,16 +4973,16 @@
       <c r="V74" s="39"/>
       <c r="W74" s="39"/>
       <c r="X74" s="39"/>
-      <c r="Y74" s="40"/>
-      <c r="Z74" s="51"/>
-      <c r="AA74" s="43"/>
-      <c r="AB74" s="43"/>
-      <c r="AC74" s="43"/>
-      <c r="AD74" s="43"/>
-      <c r="AE74" s="43"/>
-      <c r="AF74" s="43"/>
-      <c r="AG74" s="43"/>
-      <c r="AH74" s="44"/>
+      <c r="Y74" s="46"/>
+      <c r="Z74" s="52"/>
+      <c r="AA74" s="42"/>
+      <c r="AB74" s="42"/>
+      <c r="AC74" s="42"/>
+      <c r="AD74" s="42"/>
+      <c r="AE74" s="42"/>
+      <c r="AF74" s="42"/>
+      <c r="AG74" s="42"/>
+      <c r="AH74" s="43"/>
     </row>
     <row r="75" spans="1:34" ht="14.25" customHeight="1">
       <c r="A75" s="35">
@@ -4935,16 +5012,16 @@
       <c r="V75" s="39"/>
       <c r="W75" s="39"/>
       <c r="X75" s="39"/>
-      <c r="Y75" s="40"/>
-      <c r="Z75" s="51"/>
-      <c r="AA75" s="43"/>
-      <c r="AB75" s="43"/>
-      <c r="AC75" s="43"/>
-      <c r="AD75" s="43"/>
-      <c r="AE75" s="43"/>
-      <c r="AF75" s="43"/>
-      <c r="AG75" s="43"/>
-      <c r="AH75" s="44"/>
+      <c r="Y75" s="46"/>
+      <c r="Z75" s="52"/>
+      <c r="AA75" s="42"/>
+      <c r="AB75" s="42"/>
+      <c r="AC75" s="42"/>
+      <c r="AD75" s="42"/>
+      <c r="AE75" s="42"/>
+      <c r="AF75" s="42"/>
+      <c r="AG75" s="42"/>
+      <c r="AH75" s="43"/>
     </row>
     <row r="76" spans="1:34" ht="14.25" customHeight="1">
       <c r="A76" s="35">
@@ -4974,16 +5051,16 @@
       <c r="V76" s="39"/>
       <c r="W76" s="39"/>
       <c r="X76" s="39"/>
-      <c r="Y76" s="40"/>
-      <c r="Z76" s="51"/>
-      <c r="AA76" s="43"/>
-      <c r="AB76" s="43"/>
-      <c r="AC76" s="43"/>
-      <c r="AD76" s="43"/>
-      <c r="AE76" s="43"/>
-      <c r="AF76" s="43"/>
-      <c r="AG76" s="43"/>
-      <c r="AH76" s="44"/>
+      <c r="Y76" s="46"/>
+      <c r="Z76" s="52"/>
+      <c r="AA76" s="42"/>
+      <c r="AB76" s="42"/>
+      <c r="AC76" s="42"/>
+      <c r="AD76" s="42"/>
+      <c r="AE76" s="42"/>
+      <c r="AF76" s="42"/>
+      <c r="AG76" s="42"/>
+      <c r="AH76" s="43"/>
     </row>
     <row r="77" spans="1:34" ht="14.25" customHeight="1">
       <c r="A77" s="35">
@@ -5013,16 +5090,16 @@
       <c r="V77" s="39"/>
       <c r="W77" s="39"/>
       <c r="X77" s="39"/>
-      <c r="Y77" s="40"/>
-      <c r="Z77" s="51"/>
-      <c r="AA77" s="43"/>
-      <c r="AB77" s="43"/>
-      <c r="AC77" s="43"/>
-      <c r="AD77" s="43"/>
-      <c r="AE77" s="43"/>
-      <c r="AF77" s="43"/>
-      <c r="AG77" s="43"/>
-      <c r="AH77" s="44"/>
+      <c r="Y77" s="46"/>
+      <c r="Z77" s="52"/>
+      <c r="AA77" s="42"/>
+      <c r="AB77" s="42"/>
+      <c r="AC77" s="42"/>
+      <c r="AD77" s="42"/>
+      <c r="AE77" s="42"/>
+      <c r="AF77" s="42"/>
+      <c r="AG77" s="42"/>
+      <c r="AH77" s="43"/>
     </row>
     <row r="78" spans="1:34" ht="14.25" customHeight="1">
       <c r="A78" s="35">
@@ -5052,16 +5129,16 @@
       <c r="V78" s="39"/>
       <c r="W78" s="39"/>
       <c r="X78" s="39"/>
-      <c r="Y78" s="40"/>
-      <c r="Z78" s="51"/>
-      <c r="AA78" s="43"/>
-      <c r="AB78" s="43"/>
-      <c r="AC78" s="43"/>
-      <c r="AD78" s="43"/>
-      <c r="AE78" s="43"/>
-      <c r="AF78" s="43"/>
-      <c r="AG78" s="43"/>
-      <c r="AH78" s="44"/>
+      <c r="Y78" s="46"/>
+      <c r="Z78" s="52"/>
+      <c r="AA78" s="42"/>
+      <c r="AB78" s="42"/>
+      <c r="AC78" s="42"/>
+      <c r="AD78" s="42"/>
+      <c r="AE78" s="42"/>
+      <c r="AF78" s="42"/>
+      <c r="AG78" s="42"/>
+      <c r="AH78" s="43"/>
     </row>
     <row r="79" spans="1:34" ht="14.25" customHeight="1">
       <c r="A79" s="35">
@@ -5091,16 +5168,16 @@
       <c r="V79" s="39"/>
       <c r="W79" s="39"/>
       <c r="X79" s="39"/>
-      <c r="Y79" s="40"/>
-      <c r="Z79" s="51"/>
-      <c r="AA79" s="43"/>
-      <c r="AB79" s="43"/>
-      <c r="AC79" s="43"/>
-      <c r="AD79" s="43"/>
-      <c r="AE79" s="43"/>
-      <c r="AF79" s="43"/>
-      <c r="AG79" s="43"/>
-      <c r="AH79" s="44"/>
+      <c r="Y79" s="46"/>
+      <c r="Z79" s="52"/>
+      <c r="AA79" s="42"/>
+      <c r="AB79" s="42"/>
+      <c r="AC79" s="42"/>
+      <c r="AD79" s="42"/>
+      <c r="AE79" s="42"/>
+      <c r="AF79" s="42"/>
+      <c r="AG79" s="42"/>
+      <c r="AH79" s="43"/>
     </row>
     <row r="80" spans="1:34" ht="14.25" customHeight="1">
       <c r="A80" s="35">
@@ -5130,16 +5207,16 @@
       <c r="V80" s="39"/>
       <c r="W80" s="39"/>
       <c r="X80" s="39"/>
-      <c r="Y80" s="40"/>
-      <c r="Z80" s="51"/>
-      <c r="AA80" s="43"/>
-      <c r="AB80" s="43"/>
-      <c r="AC80" s="43"/>
-      <c r="AD80" s="43"/>
-      <c r="AE80" s="43"/>
-      <c r="AF80" s="43"/>
-      <c r="AG80" s="43"/>
-      <c r="AH80" s="44"/>
+      <c r="Y80" s="46"/>
+      <c r="Z80" s="52"/>
+      <c r="AA80" s="42"/>
+      <c r="AB80" s="42"/>
+      <c r="AC80" s="42"/>
+      <c r="AD80" s="42"/>
+      <c r="AE80" s="42"/>
+      <c r="AF80" s="42"/>
+      <c r="AG80" s="42"/>
+      <c r="AH80" s="43"/>
     </row>
     <row r="81" spans="1:34" ht="14.25" customHeight="1">
       <c r="A81" s="35">
@@ -5169,16 +5246,16 @@
       <c r="V81" s="39"/>
       <c r="W81" s="39"/>
       <c r="X81" s="39"/>
-      <c r="Y81" s="40"/>
-      <c r="Z81" s="51"/>
-      <c r="AA81" s="43"/>
-      <c r="AB81" s="43"/>
-      <c r="AC81" s="43"/>
-      <c r="AD81" s="43"/>
-      <c r="AE81" s="43"/>
-      <c r="AF81" s="43"/>
-      <c r="AG81" s="43"/>
-      <c r="AH81" s="44"/>
+      <c r="Y81" s="46"/>
+      <c r="Z81" s="52"/>
+      <c r="AA81" s="42"/>
+      <c r="AB81" s="42"/>
+      <c r="AC81" s="42"/>
+      <c r="AD81" s="42"/>
+      <c r="AE81" s="42"/>
+      <c r="AF81" s="42"/>
+      <c r="AG81" s="42"/>
+      <c r="AH81" s="43"/>
     </row>
     <row r="82" spans="1:34" ht="14.25" customHeight="1">
       <c r="A82" s="35">
@@ -5208,16 +5285,16 @@
       <c r="V82" s="39"/>
       <c r="W82" s="39"/>
       <c r="X82" s="39"/>
-      <c r="Y82" s="40"/>
-      <c r="Z82" s="51"/>
-      <c r="AA82" s="43"/>
-      <c r="AB82" s="43"/>
-      <c r="AC82" s="43"/>
-      <c r="AD82" s="43"/>
-      <c r="AE82" s="43"/>
-      <c r="AF82" s="43"/>
-      <c r="AG82" s="43"/>
-      <c r="AH82" s="44"/>
+      <c r="Y82" s="46"/>
+      <c r="Z82" s="52"/>
+      <c r="AA82" s="42"/>
+      <c r="AB82" s="42"/>
+      <c r="AC82" s="42"/>
+      <c r="AD82" s="42"/>
+      <c r="AE82" s="42"/>
+      <c r="AF82" s="42"/>
+      <c r="AG82" s="42"/>
+      <c r="AH82" s="43"/>
     </row>
     <row r="83" spans="1:34" ht="14.25" customHeight="1">
       <c r="A83" s="35">
@@ -5247,991 +5324,991 @@
       <c r="V83" s="39"/>
       <c r="W83" s="39"/>
       <c r="X83" s="39"/>
-      <c r="Y83" s="40"/>
-      <c r="Z83" s="51"/>
-      <c r="AA83" s="43"/>
-      <c r="AB83" s="43"/>
-      <c r="AC83" s="43"/>
-      <c r="AD83" s="43"/>
-      <c r="AE83" s="43"/>
-      <c r="AF83" s="43"/>
-      <c r="AG83" s="43"/>
-      <c r="AH83" s="44"/>
+      <c r="Y83" s="46"/>
+      <c r="Z83" s="52"/>
+      <c r="AA83" s="42"/>
+      <c r="AB83" s="42"/>
+      <c r="AC83" s="42"/>
+      <c r="AD83" s="42"/>
+      <c r="AE83" s="42"/>
+      <c r="AF83" s="42"/>
+      <c r="AG83" s="42"/>
+      <c r="AH83" s="43"/>
     </row>
     <row r="84" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A84" s="52">
+      <c r="A84" s="53">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B84" s="53"/>
-      <c r="C84" s="53"/>
-      <c r="D84" s="53"/>
-      <c r="E84" s="53"/>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53"/>
-      <c r="H84" s="53"/>
-      <c r="I84" s="53"/>
-      <c r="J84" s="53"/>
-      <c r="K84" s="53"/>
-      <c r="L84" s="53"/>
-      <c r="M84" s="53"/>
-      <c r="N84" s="53"/>
-      <c r="O84" s="53"/>
-      <c r="P84" s="53"/>
-      <c r="Q84" s="53"/>
-      <c r="R84" s="53"/>
+      <c r="B84" s="54"/>
+      <c r="C84" s="54"/>
+      <c r="D84" s="54"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="54"/>
+      <c r="I84" s="54"/>
+      <c r="J84" s="54"/>
+      <c r="K84" s="54"/>
+      <c r="L84" s="54"/>
+      <c r="M84" s="54"/>
+      <c r="N84" s="54"/>
+      <c r="O84" s="54"/>
+      <c r="P84" s="54"/>
+      <c r="Q84" s="54"/>
+      <c r="R84" s="54"/>
       <c r="S84" s="37"/>
-      <c r="T84" s="54"/>
-      <c r="U84" s="53"/>
-      <c r="V84" s="53"/>
-      <c r="W84" s="53"/>
-      <c r="X84" s="53"/>
-      <c r="Y84" s="40"/>
-      <c r="Z84" s="51"/>
-      <c r="AA84" s="43"/>
-      <c r="AB84" s="43"/>
-      <c r="AC84" s="43"/>
-      <c r="AD84" s="43"/>
-      <c r="AE84" s="43"/>
-      <c r="AF84" s="43"/>
-      <c r="AG84" s="43"/>
-      <c r="AH84" s="44"/>
+      <c r="T84" s="55"/>
+      <c r="U84" s="54"/>
+      <c r="V84" s="54"/>
+      <c r="W84" s="54"/>
+      <c r="X84" s="54"/>
+      <c r="Y84" s="46"/>
+      <c r="Z84" s="52"/>
+      <c r="AA84" s="42"/>
+      <c r="AB84" s="42"/>
+      <c r="AC84" s="42"/>
+      <c r="AD84" s="42"/>
+      <c r="AE84" s="42"/>
+      <c r="AF84" s="42"/>
+      <c r="AG84" s="42"/>
+      <c r="AH84" s="43"/>
     </row>
     <row r="85" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A85" s="55">
+      <c r="A85" s="56">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B85" s="56"/>
-      <c r="C85" s="56"/>
-      <c r="D85" s="56"/>
-      <c r="E85" s="56"/>
-      <c r="F85" s="56"/>
-      <c r="G85" s="56"/>
-      <c r="H85" s="56"/>
-      <c r="I85" s="56"/>
-      <c r="J85" s="56"/>
-      <c r="K85" s="56"/>
-      <c r="L85" s="56"/>
-      <c r="M85" s="56"/>
-      <c r="N85" s="56"/>
-      <c r="O85" s="56"/>
-      <c r="P85" s="56"/>
-      <c r="Q85" s="56"/>
-      <c r="R85" s="56"/>
-      <c r="S85" s="57"/>
-      <c r="T85" s="56"/>
-      <c r="U85" s="56"/>
-      <c r="V85" s="56"/>
-      <c r="W85" s="56"/>
-      <c r="X85" s="56"/>
-      <c r="Y85" s="57"/>
-      <c r="Z85" s="51"/>
-      <c r="AA85" s="43"/>
-      <c r="AB85" s="43"/>
-      <c r="AC85" s="43"/>
-      <c r="AD85" s="43"/>
-      <c r="AE85" s="43"/>
-      <c r="AF85" s="43"/>
-      <c r="AG85" s="43"/>
-      <c r="AH85" s="44"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="57"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="57"/>
+      <c r="F85" s="57"/>
+      <c r="G85" s="57"/>
+      <c r="H85" s="57"/>
+      <c r="I85" s="57"/>
+      <c r="J85" s="57"/>
+      <c r="K85" s="57"/>
+      <c r="L85" s="57"/>
+      <c r="M85" s="57"/>
+      <c r="N85" s="57"/>
+      <c r="O85" s="57"/>
+      <c r="P85" s="57"/>
+      <c r="Q85" s="57"/>
+      <c r="R85" s="57"/>
+      <c r="S85" s="58"/>
+      <c r="T85" s="57"/>
+      <c r="U85" s="57"/>
+      <c r="V85" s="57"/>
+      <c r="W85" s="57"/>
+      <c r="X85" s="57"/>
+      <c r="Y85" s="58"/>
+      <c r="Z85" s="52"/>
+      <c r="AA85" s="42"/>
+      <c r="AB85" s="42"/>
+      <c r="AC85" s="42"/>
+      <c r="AD85" s="42"/>
+      <c r="AE85" s="42"/>
+      <c r="AF85" s="42"/>
+      <c r="AG85" s="42"/>
+      <c r="AH85" s="43"/>
     </row>
     <row r="86" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A86" s="55">
+      <c r="A86" s="56">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B86" s="56"/>
-      <c r="C86" s="56"/>
-      <c r="D86" s="56"/>
-      <c r="E86" s="56"/>
-      <c r="F86" s="56"/>
-      <c r="G86" s="56"/>
-      <c r="H86" s="56"/>
-      <c r="I86" s="56"/>
-      <c r="J86" s="56"/>
-      <c r="K86" s="56"/>
-      <c r="L86" s="56"/>
-      <c r="M86" s="56"/>
-      <c r="N86" s="56"/>
-      <c r="O86" s="56"/>
-      <c r="P86" s="56"/>
-      <c r="Q86" s="56"/>
-      <c r="R86" s="56"/>
-      <c r="S86" s="57"/>
-      <c r="T86" s="56"/>
-      <c r="U86" s="56"/>
-      <c r="V86" s="56"/>
-      <c r="W86" s="56"/>
-      <c r="X86" s="56"/>
-      <c r="Y86" s="57"/>
-      <c r="Z86" s="51"/>
-      <c r="AA86" s="43"/>
-      <c r="AB86" s="43"/>
-      <c r="AC86" s="43"/>
-      <c r="AD86" s="43"/>
-      <c r="AE86" s="43"/>
-      <c r="AF86" s="43"/>
-      <c r="AG86" s="43"/>
-      <c r="AH86" s="44"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="57"/>
+      <c r="K86" s="57"/>
+      <c r="L86" s="57"/>
+      <c r="M86" s="57"/>
+      <c r="N86" s="57"/>
+      <c r="O86" s="57"/>
+      <c r="P86" s="57"/>
+      <c r="Q86" s="57"/>
+      <c r="R86" s="57"/>
+      <c r="S86" s="58"/>
+      <c r="T86" s="57"/>
+      <c r="U86" s="57"/>
+      <c r="V86" s="57"/>
+      <c r="W86" s="57"/>
+      <c r="X86" s="57"/>
+      <c r="Y86" s="58"/>
+      <c r="Z86" s="52"/>
+      <c r="AA86" s="42"/>
+      <c r="AB86" s="42"/>
+      <c r="AC86" s="42"/>
+      <c r="AD86" s="42"/>
+      <c r="AE86" s="42"/>
+      <c r="AF86" s="42"/>
+      <c r="AG86" s="42"/>
+      <c r="AH86" s="43"/>
     </row>
     <row r="87" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A87" s="55">
+      <c r="A87" s="56">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B87" s="56"/>
-      <c r="C87" s="56"/>
-      <c r="D87" s="56"/>
-      <c r="E87" s="56"/>
-      <c r="F87" s="56"/>
-      <c r="G87" s="56"/>
-      <c r="H87" s="56"/>
-      <c r="I87" s="56"/>
-      <c r="J87" s="56"/>
-      <c r="K87" s="56"/>
-      <c r="L87" s="56"/>
-      <c r="M87" s="56"/>
-      <c r="N87" s="56"/>
-      <c r="O87" s="56"/>
-      <c r="P87" s="56"/>
-      <c r="Q87" s="56"/>
-      <c r="R87" s="56"/>
-      <c r="S87" s="57"/>
-      <c r="T87" s="56"/>
-      <c r="U87" s="56"/>
-      <c r="V87" s="56"/>
-      <c r="W87" s="56"/>
-      <c r="X87" s="56"/>
-      <c r="Y87" s="57"/>
-      <c r="Z87" s="51"/>
-      <c r="AA87" s="43"/>
-      <c r="AB87" s="43"/>
-      <c r="AC87" s="43"/>
-      <c r="AD87" s="43"/>
-      <c r="AE87" s="43"/>
-      <c r="AF87" s="43"/>
-      <c r="AG87" s="43"/>
-      <c r="AH87" s="44"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="57"/>
+      <c r="G87" s="57"/>
+      <c r="H87" s="57"/>
+      <c r="I87" s="57"/>
+      <c r="J87" s="57"/>
+      <c r="K87" s="57"/>
+      <c r="L87" s="57"/>
+      <c r="M87" s="57"/>
+      <c r="N87" s="57"/>
+      <c r="O87" s="57"/>
+      <c r="P87" s="57"/>
+      <c r="Q87" s="57"/>
+      <c r="R87" s="57"/>
+      <c r="S87" s="58"/>
+      <c r="T87" s="57"/>
+      <c r="U87" s="57"/>
+      <c r="V87" s="57"/>
+      <c r="W87" s="57"/>
+      <c r="X87" s="57"/>
+      <c r="Y87" s="58"/>
+      <c r="Z87" s="52"/>
+      <c r="AA87" s="42"/>
+      <c r="AB87" s="42"/>
+      <c r="AC87" s="42"/>
+      <c r="AD87" s="42"/>
+      <c r="AE87" s="42"/>
+      <c r="AF87" s="42"/>
+      <c r="AG87" s="42"/>
+      <c r="AH87" s="43"/>
     </row>
     <row r="88" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A88" s="55">
+      <c r="A88" s="56">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B88" s="56"/>
-      <c r="C88" s="56"/>
-      <c r="D88" s="56"/>
-      <c r="E88" s="56"/>
-      <c r="F88" s="56"/>
-      <c r="G88" s="56"/>
-      <c r="H88" s="56"/>
-      <c r="I88" s="56"/>
-      <c r="J88" s="56"/>
-      <c r="K88" s="56"/>
-      <c r="L88" s="56"/>
-      <c r="M88" s="56"/>
-      <c r="N88" s="56"/>
-      <c r="O88" s="56"/>
-      <c r="P88" s="56"/>
-      <c r="Q88" s="56"/>
-      <c r="R88" s="56"/>
-      <c r="S88" s="57"/>
-      <c r="T88" s="56"/>
-      <c r="U88" s="56"/>
-      <c r="V88" s="56"/>
-      <c r="W88" s="56"/>
-      <c r="X88" s="56"/>
-      <c r="Y88" s="57"/>
-      <c r="Z88" s="51"/>
-      <c r="AA88" s="43"/>
-      <c r="AB88" s="43"/>
-      <c r="AC88" s="43"/>
-      <c r="AD88" s="43"/>
-      <c r="AE88" s="43"/>
-      <c r="AF88" s="43"/>
-      <c r="AG88" s="43"/>
-      <c r="AH88" s="44"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="57"/>
+      <c r="G88" s="57"/>
+      <c r="H88" s="57"/>
+      <c r="I88" s="57"/>
+      <c r="J88" s="57"/>
+      <c r="K88" s="57"/>
+      <c r="L88" s="57"/>
+      <c r="M88" s="57"/>
+      <c r="N88" s="57"/>
+      <c r="O88" s="57"/>
+      <c r="P88" s="57"/>
+      <c r="Q88" s="57"/>
+      <c r="R88" s="57"/>
+      <c r="S88" s="58"/>
+      <c r="T88" s="57"/>
+      <c r="U88" s="57"/>
+      <c r="V88" s="57"/>
+      <c r="W88" s="57"/>
+      <c r="X88" s="57"/>
+      <c r="Y88" s="58"/>
+      <c r="Z88" s="52"/>
+      <c r="AA88" s="42"/>
+      <c r="AB88" s="42"/>
+      <c r="AC88" s="42"/>
+      <c r="AD88" s="42"/>
+      <c r="AE88" s="42"/>
+      <c r="AF88" s="42"/>
+      <c r="AG88" s="42"/>
+      <c r="AH88" s="43"/>
     </row>
     <row r="89" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A89" s="55">
+      <c r="A89" s="56">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B89" s="56"/>
-      <c r="C89" s="56"/>
-      <c r="D89" s="56"/>
-      <c r="E89" s="56"/>
-      <c r="F89" s="56"/>
-      <c r="G89" s="56"/>
-      <c r="H89" s="56"/>
-      <c r="I89" s="56"/>
-      <c r="J89" s="56"/>
-      <c r="K89" s="56"/>
-      <c r="L89" s="56"/>
-      <c r="M89" s="56"/>
-      <c r="N89" s="56"/>
-      <c r="O89" s="56"/>
-      <c r="P89" s="56"/>
-      <c r="Q89" s="56"/>
-      <c r="R89" s="56"/>
-      <c r="S89" s="57"/>
-      <c r="T89" s="56"/>
-      <c r="U89" s="56"/>
-      <c r="V89" s="56"/>
-      <c r="W89" s="56"/>
-      <c r="X89" s="56"/>
-      <c r="Y89" s="57"/>
-      <c r="Z89" s="51"/>
-      <c r="AA89" s="43"/>
-      <c r="AB89" s="43"/>
-      <c r="AC89" s="43"/>
-      <c r="AD89" s="43"/>
-      <c r="AE89" s="43"/>
-      <c r="AF89" s="43"/>
-      <c r="AG89" s="43"/>
-      <c r="AH89" s="44"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="57"/>
+      <c r="D89" s="57"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="57"/>
+      <c r="G89" s="57"/>
+      <c r="H89" s="57"/>
+      <c r="I89" s="57"/>
+      <c r="J89" s="57"/>
+      <c r="K89" s="57"/>
+      <c r="L89" s="57"/>
+      <c r="M89" s="57"/>
+      <c r="N89" s="57"/>
+      <c r="O89" s="57"/>
+      <c r="P89" s="57"/>
+      <c r="Q89" s="57"/>
+      <c r="R89" s="57"/>
+      <c r="S89" s="58"/>
+      <c r="T89" s="57"/>
+      <c r="U89" s="57"/>
+      <c r="V89" s="57"/>
+      <c r="W89" s="57"/>
+      <c r="X89" s="57"/>
+      <c r="Y89" s="58"/>
+      <c r="Z89" s="52"/>
+      <c r="AA89" s="42"/>
+      <c r="AB89" s="42"/>
+      <c r="AC89" s="42"/>
+      <c r="AD89" s="42"/>
+      <c r="AE89" s="42"/>
+      <c r="AF89" s="42"/>
+      <c r="AG89" s="42"/>
+      <c r="AH89" s="43"/>
     </row>
     <row r="90" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A90" s="55">
+      <c r="A90" s="56">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B90" s="56"/>
-      <c r="C90" s="56"/>
-      <c r="D90" s="56"/>
-      <c r="E90" s="56"/>
-      <c r="F90" s="56"/>
-      <c r="G90" s="56"/>
-      <c r="H90" s="56"/>
-      <c r="I90" s="56"/>
-      <c r="J90" s="56"/>
-      <c r="K90" s="56"/>
-      <c r="L90" s="56"/>
-      <c r="M90" s="56"/>
-      <c r="N90" s="56"/>
-      <c r="O90" s="56"/>
-      <c r="P90" s="56"/>
-      <c r="Q90" s="56"/>
-      <c r="R90" s="56"/>
-      <c r="S90" s="57"/>
-      <c r="T90" s="56"/>
-      <c r="U90" s="56"/>
-      <c r="V90" s="56"/>
-      <c r="W90" s="56"/>
-      <c r="X90" s="56"/>
-      <c r="Y90" s="57"/>
-      <c r="Z90" s="51"/>
-      <c r="AA90" s="43"/>
-      <c r="AB90" s="43"/>
-      <c r="AC90" s="43"/>
-      <c r="AD90" s="43"/>
-      <c r="AE90" s="43"/>
-      <c r="AF90" s="43"/>
-      <c r="AG90" s="43"/>
-      <c r="AH90" s="44"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="57"/>
+      <c r="G90" s="57"/>
+      <c r="H90" s="57"/>
+      <c r="I90" s="57"/>
+      <c r="J90" s="57"/>
+      <c r="K90" s="57"/>
+      <c r="L90" s="57"/>
+      <c r="M90" s="57"/>
+      <c r="N90" s="57"/>
+      <c r="O90" s="57"/>
+      <c r="P90" s="57"/>
+      <c r="Q90" s="57"/>
+      <c r="R90" s="57"/>
+      <c r="S90" s="58"/>
+      <c r="T90" s="57"/>
+      <c r="U90" s="57"/>
+      <c r="V90" s="57"/>
+      <c r="W90" s="57"/>
+      <c r="X90" s="57"/>
+      <c r="Y90" s="58"/>
+      <c r="Z90" s="52"/>
+      <c r="AA90" s="42"/>
+      <c r="AB90" s="42"/>
+      <c r="AC90" s="42"/>
+      <c r="AD90" s="42"/>
+      <c r="AE90" s="42"/>
+      <c r="AF90" s="42"/>
+      <c r="AG90" s="42"/>
+      <c r="AH90" s="43"/>
     </row>
     <row r="91" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A91" s="55">
+      <c r="A91" s="56">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B91" s="56"/>
-      <c r="C91" s="56"/>
-      <c r="D91" s="56"/>
-      <c r="E91" s="56"/>
-      <c r="F91" s="56"/>
-      <c r="G91" s="56"/>
-      <c r="H91" s="56"/>
-      <c r="I91" s="56"/>
-      <c r="J91" s="56"/>
-      <c r="K91" s="56"/>
-      <c r="L91" s="56"/>
-      <c r="M91" s="56"/>
-      <c r="N91" s="56"/>
-      <c r="O91" s="56"/>
-      <c r="P91" s="56"/>
-      <c r="Q91" s="56"/>
-      <c r="R91" s="56"/>
-      <c r="S91" s="57"/>
-      <c r="T91" s="56"/>
-      <c r="U91" s="56"/>
-      <c r="V91" s="56"/>
-      <c r="W91" s="56"/>
-      <c r="X91" s="56"/>
-      <c r="Y91" s="57"/>
-      <c r="Z91" s="51"/>
-      <c r="AA91" s="43"/>
-      <c r="AB91" s="43"/>
-      <c r="AC91" s="43"/>
-      <c r="AD91" s="43"/>
-      <c r="AE91" s="43"/>
-      <c r="AF91" s="43"/>
-      <c r="AG91" s="43"/>
-      <c r="AH91" s="44"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="57"/>
+      <c r="D91" s="57"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="57"/>
+      <c r="G91" s="57"/>
+      <c r="H91" s="57"/>
+      <c r="I91" s="57"/>
+      <c r="J91" s="57"/>
+      <c r="K91" s="57"/>
+      <c r="L91" s="57"/>
+      <c r="M91" s="57"/>
+      <c r="N91" s="57"/>
+      <c r="O91" s="57"/>
+      <c r="P91" s="57"/>
+      <c r="Q91" s="57"/>
+      <c r="R91" s="57"/>
+      <c r="S91" s="58"/>
+      <c r="T91" s="57"/>
+      <c r="U91" s="57"/>
+      <c r="V91" s="57"/>
+      <c r="W91" s="57"/>
+      <c r="X91" s="57"/>
+      <c r="Y91" s="58"/>
+      <c r="Z91" s="52"/>
+      <c r="AA91" s="42"/>
+      <c r="AB91" s="42"/>
+      <c r="AC91" s="42"/>
+      <c r="AD91" s="42"/>
+      <c r="AE91" s="42"/>
+      <c r="AF91" s="42"/>
+      <c r="AG91" s="42"/>
+      <c r="AH91" s="43"/>
     </row>
     <row r="92" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A92" s="55">
+      <c r="A92" s="56">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="B92" s="56"/>
-      <c r="C92" s="56"/>
-      <c r="D92" s="56"/>
-      <c r="E92" s="56"/>
-      <c r="F92" s="56"/>
-      <c r="G92" s="56"/>
-      <c r="H92" s="56"/>
-      <c r="I92" s="56"/>
-      <c r="J92" s="56"/>
-      <c r="K92" s="56"/>
-      <c r="L92" s="56"/>
-      <c r="M92" s="56"/>
-      <c r="N92" s="56"/>
-      <c r="O92" s="56"/>
-      <c r="P92" s="56"/>
-      <c r="Q92" s="56"/>
-      <c r="R92" s="56"/>
-      <c r="S92" s="57"/>
-      <c r="T92" s="56"/>
-      <c r="U92" s="56"/>
-      <c r="V92" s="56"/>
-      <c r="W92" s="56"/>
-      <c r="X92" s="56"/>
-      <c r="Y92" s="57"/>
-      <c r="Z92" s="51"/>
-      <c r="AA92" s="43"/>
-      <c r="AB92" s="43"/>
-      <c r="AC92" s="43"/>
-      <c r="AD92" s="43"/>
-      <c r="AE92" s="43"/>
-      <c r="AF92" s="43"/>
-      <c r="AG92" s="43"/>
-      <c r="AH92" s="44"/>
+      <c r="B92" s="57"/>
+      <c r="C92" s="57"/>
+      <c r="D92" s="57"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="57"/>
+      <c r="G92" s="57"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="57"/>
+      <c r="J92" s="57"/>
+      <c r="K92" s="57"/>
+      <c r="L92" s="57"/>
+      <c r="M92" s="57"/>
+      <c r="N92" s="57"/>
+      <c r="O92" s="57"/>
+      <c r="P92" s="57"/>
+      <c r="Q92" s="57"/>
+      <c r="R92" s="57"/>
+      <c r="S92" s="58"/>
+      <c r="T92" s="57"/>
+      <c r="U92" s="57"/>
+      <c r="V92" s="57"/>
+      <c r="W92" s="57"/>
+      <c r="X92" s="57"/>
+      <c r="Y92" s="58"/>
+      <c r="Z92" s="52"/>
+      <c r="AA92" s="42"/>
+      <c r="AB92" s="42"/>
+      <c r="AC92" s="42"/>
+      <c r="AD92" s="42"/>
+      <c r="AE92" s="42"/>
+      <c r="AF92" s="42"/>
+      <c r="AG92" s="42"/>
+      <c r="AH92" s="43"/>
     </row>
     <row r="93" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A93" s="55">
+      <c r="A93" s="56">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="B93" s="56"/>
-      <c r="C93" s="56"/>
-      <c r="D93" s="56"/>
-      <c r="E93" s="56"/>
-      <c r="F93" s="56"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="56"/>
-      <c r="I93" s="56"/>
-      <c r="J93" s="56"/>
-      <c r="K93" s="56"/>
-      <c r="L93" s="56"/>
-      <c r="M93" s="56"/>
-      <c r="N93" s="56"/>
-      <c r="O93" s="56"/>
-      <c r="P93" s="56"/>
-      <c r="Q93" s="56"/>
-      <c r="R93" s="56"/>
-      <c r="S93" s="57"/>
-      <c r="T93" s="56"/>
-      <c r="U93" s="56"/>
-      <c r="V93" s="56"/>
-      <c r="W93" s="56"/>
-      <c r="X93" s="56"/>
-      <c r="Y93" s="57"/>
-      <c r="Z93" s="51"/>
-      <c r="AA93" s="43"/>
-      <c r="AB93" s="43"/>
-      <c r="AC93" s="43"/>
-      <c r="AD93" s="43"/>
-      <c r="AE93" s="43"/>
-      <c r="AF93" s="43"/>
-      <c r="AG93" s="43"/>
-      <c r="AH93" s="44"/>
+      <c r="B93" s="57"/>
+      <c r="C93" s="57"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="57"/>
+      <c r="L93" s="57"/>
+      <c r="M93" s="57"/>
+      <c r="N93" s="57"/>
+      <c r="O93" s="57"/>
+      <c r="P93" s="57"/>
+      <c r="Q93" s="57"/>
+      <c r="R93" s="57"/>
+      <c r="S93" s="58"/>
+      <c r="T93" s="57"/>
+      <c r="U93" s="57"/>
+      <c r="V93" s="57"/>
+      <c r="W93" s="57"/>
+      <c r="X93" s="57"/>
+      <c r="Y93" s="58"/>
+      <c r="Z93" s="52"/>
+      <c r="AA93" s="42"/>
+      <c r="AB93" s="42"/>
+      <c r="AC93" s="42"/>
+      <c r="AD93" s="42"/>
+      <c r="AE93" s="42"/>
+      <c r="AF93" s="42"/>
+      <c r="AG93" s="42"/>
+      <c r="AH93" s="43"/>
     </row>
     <row r="94" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A94" s="55">
+      <c r="A94" s="56">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="B94" s="56"/>
-      <c r="C94" s="56"/>
-      <c r="D94" s="56"/>
-      <c r="E94" s="56"/>
-      <c r="F94" s="56"/>
-      <c r="G94" s="56"/>
-      <c r="H94" s="56"/>
-      <c r="I94" s="56"/>
-      <c r="J94" s="56"/>
-      <c r="K94" s="56"/>
-      <c r="L94" s="56"/>
-      <c r="M94" s="56"/>
-      <c r="N94" s="56"/>
-      <c r="O94" s="56"/>
-      <c r="P94" s="56"/>
-      <c r="Q94" s="56"/>
-      <c r="R94" s="56"/>
-      <c r="S94" s="57"/>
-      <c r="T94" s="56"/>
-      <c r="U94" s="56"/>
-      <c r="V94" s="56"/>
-      <c r="W94" s="56"/>
-      <c r="X94" s="56"/>
-      <c r="Y94" s="57"/>
-      <c r="Z94" s="51"/>
-      <c r="AA94" s="43"/>
-      <c r="AB94" s="43"/>
-      <c r="AC94" s="43"/>
-      <c r="AD94" s="43"/>
-      <c r="AE94" s="43"/>
-      <c r="AF94" s="43"/>
-      <c r="AG94" s="43"/>
-      <c r="AH94" s="44"/>
+      <c r="B94" s="57"/>
+      <c r="C94" s="57"/>
+      <c r="D94" s="57"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="57"/>
+      <c r="G94" s="57"/>
+      <c r="H94" s="57"/>
+      <c r="I94" s="57"/>
+      <c r="J94" s="57"/>
+      <c r="K94" s="57"/>
+      <c r="L94" s="57"/>
+      <c r="M94" s="57"/>
+      <c r="N94" s="57"/>
+      <c r="O94" s="57"/>
+      <c r="P94" s="57"/>
+      <c r="Q94" s="57"/>
+      <c r="R94" s="57"/>
+      <c r="S94" s="58"/>
+      <c r="T94" s="57"/>
+      <c r="U94" s="57"/>
+      <c r="V94" s="57"/>
+      <c r="W94" s="57"/>
+      <c r="X94" s="57"/>
+      <c r="Y94" s="58"/>
+      <c r="Z94" s="52"/>
+      <c r="AA94" s="42"/>
+      <c r="AB94" s="42"/>
+      <c r="AC94" s="42"/>
+      <c r="AD94" s="42"/>
+      <c r="AE94" s="42"/>
+      <c r="AF94" s="42"/>
+      <c r="AG94" s="42"/>
+      <c r="AH94" s="43"/>
     </row>
     <row r="95" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A95" s="55">
+      <c r="A95" s="56">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="B95" s="56"/>
-      <c r="C95" s="56"/>
-      <c r="D95" s="56"/>
-      <c r="E95" s="56"/>
-      <c r="F95" s="56"/>
-      <c r="G95" s="56"/>
-      <c r="H95" s="56"/>
-      <c r="I95" s="56"/>
-      <c r="J95" s="56"/>
-      <c r="K95" s="56"/>
-      <c r="L95" s="56"/>
-      <c r="M95" s="56"/>
-      <c r="N95" s="56"/>
-      <c r="O95" s="56"/>
-      <c r="P95" s="56"/>
-      <c r="Q95" s="56"/>
-      <c r="R95" s="56"/>
-      <c r="S95" s="57"/>
-      <c r="T95" s="56"/>
-      <c r="U95" s="56"/>
-      <c r="V95" s="56"/>
-      <c r="W95" s="56"/>
-      <c r="X95" s="56"/>
-      <c r="Y95" s="57"/>
-      <c r="Z95" s="51"/>
-      <c r="AA95" s="43"/>
-      <c r="AB95" s="43"/>
-      <c r="AC95" s="43"/>
-      <c r="AD95" s="43"/>
-      <c r="AE95" s="43"/>
-      <c r="AF95" s="43"/>
-      <c r="AG95" s="43"/>
-      <c r="AH95" s="44"/>
+      <c r="B95" s="57"/>
+      <c r="C95" s="57"/>
+      <c r="D95" s="57"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="57"/>
+      <c r="G95" s="57"/>
+      <c r="H95" s="57"/>
+      <c r="I95" s="57"/>
+      <c r="J95" s="57"/>
+      <c r="K95" s="57"/>
+      <c r="L95" s="57"/>
+      <c r="M95" s="57"/>
+      <c r="N95" s="57"/>
+      <c r="O95" s="57"/>
+      <c r="P95" s="57"/>
+      <c r="Q95" s="57"/>
+      <c r="R95" s="57"/>
+      <c r="S95" s="58"/>
+      <c r="T95" s="57"/>
+      <c r="U95" s="57"/>
+      <c r="V95" s="57"/>
+      <c r="W95" s="57"/>
+      <c r="X95" s="57"/>
+      <c r="Y95" s="58"/>
+      <c r="Z95" s="52"/>
+      <c r="AA95" s="42"/>
+      <c r="AB95" s="42"/>
+      <c r="AC95" s="42"/>
+      <c r="AD95" s="42"/>
+      <c r="AE95" s="42"/>
+      <c r="AF95" s="42"/>
+      <c r="AG95" s="42"/>
+      <c r="AH95" s="43"/>
     </row>
     <row r="96" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A96" s="55">
+      <c r="A96" s="56">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="B96" s="56"/>
-      <c r="C96" s="56"/>
-      <c r="D96" s="56"/>
-      <c r="E96" s="56"/>
-      <c r="F96" s="56"/>
-      <c r="G96" s="56"/>
-      <c r="H96" s="56"/>
-      <c r="I96" s="56"/>
-      <c r="J96" s="56"/>
-      <c r="K96" s="56"/>
-      <c r="L96" s="56"/>
-      <c r="M96" s="56"/>
-      <c r="N96" s="56"/>
-      <c r="O96" s="56"/>
-      <c r="P96" s="56"/>
-      <c r="Q96" s="56"/>
-      <c r="R96" s="56"/>
-      <c r="S96" s="57"/>
-      <c r="T96" s="56"/>
-      <c r="U96" s="56"/>
-      <c r="V96" s="56"/>
-      <c r="W96" s="56"/>
-      <c r="X96" s="56"/>
-      <c r="Y96" s="57"/>
-      <c r="Z96" s="51"/>
-      <c r="AA96" s="43"/>
-      <c r="AB96" s="43"/>
-      <c r="AC96" s="43"/>
-      <c r="AD96" s="43"/>
-      <c r="AE96" s="43"/>
-      <c r="AF96" s="43"/>
-      <c r="AG96" s="43"/>
-      <c r="AH96" s="44"/>
+      <c r="B96" s="57"/>
+      <c r="C96" s="57"/>
+      <c r="D96" s="57"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="57"/>
+      <c r="G96" s="57"/>
+      <c r="H96" s="57"/>
+      <c r="I96" s="57"/>
+      <c r="J96" s="57"/>
+      <c r="K96" s="57"/>
+      <c r="L96" s="57"/>
+      <c r="M96" s="57"/>
+      <c r="N96" s="57"/>
+      <c r="O96" s="57"/>
+      <c r="P96" s="57"/>
+      <c r="Q96" s="57"/>
+      <c r="R96" s="57"/>
+      <c r="S96" s="58"/>
+      <c r="T96" s="57"/>
+      <c r="U96" s="57"/>
+      <c r="V96" s="57"/>
+      <c r="W96" s="57"/>
+      <c r="X96" s="57"/>
+      <c r="Y96" s="58"/>
+      <c r="Z96" s="52"/>
+      <c r="AA96" s="42"/>
+      <c r="AB96" s="42"/>
+      <c r="AC96" s="42"/>
+      <c r="AD96" s="42"/>
+      <c r="AE96" s="42"/>
+      <c r="AF96" s="42"/>
+      <c r="AG96" s="42"/>
+      <c r="AH96" s="43"/>
     </row>
     <row r="97" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A97" s="55">
+      <c r="A97" s="56">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="B97" s="56"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="56"/>
-      <c r="E97" s="56"/>
-      <c r="F97" s="56"/>
-      <c r="G97" s="56"/>
-      <c r="H97" s="56"/>
-      <c r="I97" s="56"/>
-      <c r="J97" s="56"/>
-      <c r="K97" s="56"/>
-      <c r="L97" s="56"/>
-      <c r="M97" s="56"/>
-      <c r="N97" s="56"/>
-      <c r="O97" s="56"/>
-      <c r="P97" s="56"/>
-      <c r="Q97" s="56"/>
-      <c r="R97" s="56"/>
-      <c r="S97" s="57"/>
-      <c r="T97" s="56"/>
-      <c r="U97" s="56"/>
-      <c r="V97" s="56"/>
-      <c r="W97" s="56"/>
-      <c r="X97" s="56"/>
-      <c r="Y97" s="57"/>
-      <c r="Z97" s="51"/>
-      <c r="AA97" s="43"/>
-      <c r="AB97" s="43"/>
-      <c r="AC97" s="43"/>
-      <c r="AD97" s="43"/>
-      <c r="AE97" s="43"/>
-      <c r="AF97" s="43"/>
-      <c r="AG97" s="43"/>
-      <c r="AH97" s="44"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="57"/>
+      <c r="J97" s="57"/>
+      <c r="K97" s="57"/>
+      <c r="L97" s="57"/>
+      <c r="M97" s="57"/>
+      <c r="N97" s="57"/>
+      <c r="O97" s="57"/>
+      <c r="P97" s="57"/>
+      <c r="Q97" s="57"/>
+      <c r="R97" s="57"/>
+      <c r="S97" s="58"/>
+      <c r="T97" s="57"/>
+      <c r="U97" s="57"/>
+      <c r="V97" s="57"/>
+      <c r="W97" s="57"/>
+      <c r="X97" s="57"/>
+      <c r="Y97" s="58"/>
+      <c r="Z97" s="52"/>
+      <c r="AA97" s="42"/>
+      <c r="AB97" s="42"/>
+      <c r="AC97" s="42"/>
+      <c r="AD97" s="42"/>
+      <c r="AE97" s="42"/>
+      <c r="AF97" s="42"/>
+      <c r="AG97" s="42"/>
+      <c r="AH97" s="43"/>
     </row>
     <row r="98" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A98" s="55">
+      <c r="A98" s="56">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="B98" s="56"/>
-      <c r="C98" s="56"/>
-      <c r="D98" s="56"/>
-      <c r="E98" s="56"/>
-      <c r="F98" s="56"/>
-      <c r="G98" s="56"/>
-      <c r="H98" s="56"/>
-      <c r="I98" s="56"/>
-      <c r="J98" s="56"/>
-      <c r="K98" s="56"/>
-      <c r="L98" s="56"/>
-      <c r="M98" s="56"/>
-      <c r="N98" s="56"/>
-      <c r="O98" s="56"/>
-      <c r="P98" s="56"/>
-      <c r="Q98" s="56"/>
-      <c r="R98" s="56"/>
-      <c r="S98" s="57"/>
-      <c r="T98" s="56"/>
-      <c r="U98" s="56"/>
-      <c r="V98" s="56"/>
-      <c r="W98" s="56"/>
-      <c r="X98" s="56"/>
-      <c r="Y98" s="57"/>
-      <c r="Z98" s="51"/>
-      <c r="AA98" s="43"/>
-      <c r="AB98" s="43"/>
-      <c r="AC98" s="43"/>
-      <c r="AD98" s="43"/>
-      <c r="AE98" s="43"/>
-      <c r="AF98" s="43"/>
-      <c r="AG98" s="43"/>
-      <c r="AH98" s="44"/>
+      <c r="B98" s="57"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
+      <c r="H98" s="57"/>
+      <c r="I98" s="57"/>
+      <c r="J98" s="57"/>
+      <c r="K98" s="57"/>
+      <c r="L98" s="57"/>
+      <c r="M98" s="57"/>
+      <c r="N98" s="57"/>
+      <c r="O98" s="57"/>
+      <c r="P98" s="57"/>
+      <c r="Q98" s="57"/>
+      <c r="R98" s="57"/>
+      <c r="S98" s="58"/>
+      <c r="T98" s="57"/>
+      <c r="U98" s="57"/>
+      <c r="V98" s="57"/>
+      <c r="W98" s="57"/>
+      <c r="X98" s="57"/>
+      <c r="Y98" s="58"/>
+      <c r="Z98" s="52"/>
+      <c r="AA98" s="42"/>
+      <c r="AB98" s="42"/>
+      <c r="AC98" s="42"/>
+      <c r="AD98" s="42"/>
+      <c r="AE98" s="42"/>
+      <c r="AF98" s="42"/>
+      <c r="AG98" s="42"/>
+      <c r="AH98" s="43"/>
     </row>
     <row r="99" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A99" s="55">
+      <c r="A99" s="56">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="B99" s="56"/>
-      <c r="C99" s="56"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="56"/>
-      <c r="F99" s="56"/>
-      <c r="G99" s="56"/>
-      <c r="H99" s="56"/>
-      <c r="I99" s="56"/>
-      <c r="J99" s="56"/>
-      <c r="K99" s="56"/>
-      <c r="L99" s="56"/>
-      <c r="M99" s="56"/>
-      <c r="N99" s="56"/>
-      <c r="O99" s="56"/>
-      <c r="P99" s="56"/>
-      <c r="Q99" s="56"/>
-      <c r="R99" s="56"/>
-      <c r="S99" s="57"/>
-      <c r="T99" s="56"/>
-      <c r="U99" s="56"/>
-      <c r="V99" s="56"/>
-      <c r="W99" s="56"/>
-      <c r="X99" s="56"/>
-      <c r="Y99" s="57"/>
-      <c r="Z99" s="51"/>
-      <c r="AA99" s="43"/>
-      <c r="AB99" s="43"/>
-      <c r="AC99" s="43"/>
-      <c r="AD99" s="43"/>
-      <c r="AE99" s="43"/>
-      <c r="AF99" s="43"/>
-      <c r="AG99" s="43"/>
-      <c r="AH99" s="44"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="57"/>
+      <c r="D99" s="57"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
+      <c r="G99" s="57"/>
+      <c r="H99" s="57"/>
+      <c r="I99" s="57"/>
+      <c r="J99" s="57"/>
+      <c r="K99" s="57"/>
+      <c r="L99" s="57"/>
+      <c r="M99" s="57"/>
+      <c r="N99" s="57"/>
+      <c r="O99" s="57"/>
+      <c r="P99" s="57"/>
+      <c r="Q99" s="57"/>
+      <c r="R99" s="57"/>
+      <c r="S99" s="58"/>
+      <c r="T99" s="57"/>
+      <c r="U99" s="57"/>
+      <c r="V99" s="57"/>
+      <c r="W99" s="57"/>
+      <c r="X99" s="57"/>
+      <c r="Y99" s="58"/>
+      <c r="Z99" s="52"/>
+      <c r="AA99" s="42"/>
+      <c r="AB99" s="42"/>
+      <c r="AC99" s="42"/>
+      <c r="AD99" s="42"/>
+      <c r="AE99" s="42"/>
+      <c r="AF99" s="42"/>
+      <c r="AG99" s="42"/>
+      <c r="AH99" s="43"/>
     </row>
     <row r="100" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A100" s="55">
+      <c r="A100" s="56">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="B100" s="56"/>
-      <c r="C100" s="56"/>
-      <c r="D100" s="56"/>
-      <c r="E100" s="56"/>
-      <c r="F100" s="56"/>
-      <c r="G100" s="56"/>
-      <c r="H100" s="56"/>
-      <c r="I100" s="56"/>
-      <c r="J100" s="56"/>
-      <c r="K100" s="56"/>
-      <c r="L100" s="56"/>
-      <c r="M100" s="56"/>
-      <c r="N100" s="56"/>
-      <c r="O100" s="56"/>
-      <c r="P100" s="56"/>
-      <c r="Q100" s="56"/>
-      <c r="R100" s="56"/>
-      <c r="S100" s="57"/>
-      <c r="T100" s="56"/>
-      <c r="U100" s="56"/>
-      <c r="V100" s="56"/>
-      <c r="W100" s="56"/>
-      <c r="X100" s="56"/>
-      <c r="Y100" s="57"/>
-      <c r="Z100" s="51"/>
-      <c r="AA100" s="43"/>
-      <c r="AB100" s="43"/>
-      <c r="AC100" s="43"/>
-      <c r="AD100" s="43"/>
-      <c r="AE100" s="43"/>
-      <c r="AF100" s="43"/>
-      <c r="AG100" s="43"/>
-      <c r="AH100" s="44"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
+      <c r="L100" s="57"/>
+      <c r="M100" s="57"/>
+      <c r="N100" s="57"/>
+      <c r="O100" s="57"/>
+      <c r="P100" s="57"/>
+      <c r="Q100" s="57"/>
+      <c r="R100" s="57"/>
+      <c r="S100" s="58"/>
+      <c r="T100" s="57"/>
+      <c r="U100" s="57"/>
+      <c r="V100" s="57"/>
+      <c r="W100" s="57"/>
+      <c r="X100" s="57"/>
+      <c r="Y100" s="58"/>
+      <c r="Z100" s="52"/>
+      <c r="AA100" s="42"/>
+      <c r="AB100" s="42"/>
+      <c r="AC100" s="42"/>
+      <c r="AD100" s="42"/>
+      <c r="AE100" s="42"/>
+      <c r="AF100" s="42"/>
+      <c r="AG100" s="42"/>
+      <c r="AH100" s="43"/>
     </row>
     <row r="101" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A101" s="55">
+      <c r="A101" s="56">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="B101" s="56"/>
-      <c r="C101" s="56"/>
-      <c r="D101" s="56"/>
-      <c r="E101" s="56"/>
-      <c r="F101" s="56"/>
-      <c r="G101" s="56"/>
-      <c r="H101" s="56"/>
-      <c r="I101" s="56"/>
-      <c r="J101" s="56"/>
-      <c r="K101" s="56"/>
-      <c r="L101" s="56"/>
-      <c r="M101" s="56"/>
-      <c r="N101" s="56"/>
-      <c r="O101" s="56"/>
-      <c r="P101" s="56"/>
-      <c r="Q101" s="56"/>
-      <c r="R101" s="56"/>
-      <c r="S101" s="57"/>
-      <c r="T101" s="56"/>
-      <c r="U101" s="56"/>
-      <c r="V101" s="56"/>
-      <c r="W101" s="56"/>
-      <c r="X101" s="56"/>
-      <c r="Y101" s="57"/>
-      <c r="Z101" s="51"/>
-      <c r="AA101" s="43"/>
-      <c r="AB101" s="43"/>
-      <c r="AC101" s="43"/>
-      <c r="AD101" s="43"/>
-      <c r="AE101" s="43"/>
-      <c r="AF101" s="43"/>
-      <c r="AG101" s="43"/>
-      <c r="AH101" s="44"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="57"/>
+      <c r="D101" s="57"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="57"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="57"/>
+      <c r="I101" s="57"/>
+      <c r="J101" s="57"/>
+      <c r="K101" s="57"/>
+      <c r="L101" s="57"/>
+      <c r="M101" s="57"/>
+      <c r="N101" s="57"/>
+      <c r="O101" s="57"/>
+      <c r="P101" s="57"/>
+      <c r="Q101" s="57"/>
+      <c r="R101" s="57"/>
+      <c r="S101" s="58"/>
+      <c r="T101" s="57"/>
+      <c r="U101" s="57"/>
+      <c r="V101" s="57"/>
+      <c r="W101" s="57"/>
+      <c r="X101" s="57"/>
+      <c r="Y101" s="58"/>
+      <c r="Z101" s="52"/>
+      <c r="AA101" s="42"/>
+      <c r="AB101" s="42"/>
+      <c r="AC101" s="42"/>
+      <c r="AD101" s="42"/>
+      <c r="AE101" s="42"/>
+      <c r="AF101" s="42"/>
+      <c r="AG101" s="42"/>
+      <c r="AH101" s="43"/>
     </row>
     <row r="102" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A102" s="55">
+      <c r="A102" s="56">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="B102" s="56"/>
-      <c r="C102" s="56"/>
-      <c r="D102" s="56"/>
-      <c r="E102" s="56"/>
-      <c r="F102" s="56"/>
-      <c r="G102" s="56"/>
-      <c r="H102" s="56"/>
-      <c r="I102" s="56"/>
-      <c r="J102" s="56"/>
-      <c r="K102" s="56"/>
-      <c r="L102" s="56"/>
-      <c r="M102" s="56"/>
-      <c r="N102" s="56"/>
-      <c r="O102" s="56"/>
-      <c r="P102" s="56"/>
-      <c r="Q102" s="56"/>
-      <c r="R102" s="56"/>
-      <c r="S102" s="57"/>
-      <c r="T102" s="56"/>
-      <c r="U102" s="56"/>
-      <c r="V102" s="56"/>
-      <c r="W102" s="56"/>
-      <c r="X102" s="56"/>
-      <c r="Y102" s="57"/>
-      <c r="Z102" s="51"/>
-      <c r="AA102" s="43"/>
-      <c r="AB102" s="43"/>
-      <c r="AC102" s="43"/>
-      <c r="AD102" s="43"/>
-      <c r="AE102" s="43"/>
-      <c r="AF102" s="43"/>
-      <c r="AG102" s="43"/>
-      <c r="AH102" s="44"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="57"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
+      <c r="I102" s="57"/>
+      <c r="J102" s="57"/>
+      <c r="K102" s="57"/>
+      <c r="L102" s="57"/>
+      <c r="M102" s="57"/>
+      <c r="N102" s="57"/>
+      <c r="O102" s="57"/>
+      <c r="P102" s="57"/>
+      <c r="Q102" s="57"/>
+      <c r="R102" s="57"/>
+      <c r="S102" s="58"/>
+      <c r="T102" s="57"/>
+      <c r="U102" s="57"/>
+      <c r="V102" s="57"/>
+      <c r="W102" s="57"/>
+      <c r="X102" s="57"/>
+      <c r="Y102" s="58"/>
+      <c r="Z102" s="52"/>
+      <c r="AA102" s="42"/>
+      <c r="AB102" s="42"/>
+      <c r="AC102" s="42"/>
+      <c r="AD102" s="42"/>
+      <c r="AE102" s="42"/>
+      <c r="AF102" s="42"/>
+      <c r="AG102" s="42"/>
+      <c r="AH102" s="43"/>
     </row>
     <row r="103" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A103" s="55">
+      <c r="A103" s="56">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="B103" s="56"/>
-      <c r="C103" s="56"/>
-      <c r="D103" s="56"/>
-      <c r="E103" s="56"/>
-      <c r="F103" s="56"/>
-      <c r="G103" s="56"/>
-      <c r="H103" s="56"/>
-      <c r="I103" s="56"/>
-      <c r="J103" s="56"/>
-      <c r="K103" s="56"/>
-      <c r="L103" s="56"/>
-      <c r="M103" s="56"/>
-      <c r="N103" s="56"/>
-      <c r="O103" s="56"/>
-      <c r="P103" s="56"/>
-      <c r="Q103" s="56"/>
-      <c r="R103" s="56"/>
-      <c r="S103" s="57"/>
-      <c r="T103" s="56"/>
-      <c r="U103" s="56"/>
-      <c r="V103" s="56"/>
-      <c r="W103" s="56"/>
-      <c r="X103" s="56"/>
-      <c r="Y103" s="57"/>
-      <c r="Z103" s="51"/>
-      <c r="AA103" s="43"/>
-      <c r="AB103" s="43"/>
-      <c r="AC103" s="43"/>
-      <c r="AD103" s="43"/>
-      <c r="AE103" s="43"/>
-      <c r="AF103" s="43"/>
-      <c r="AG103" s="43"/>
-      <c r="AH103" s="44"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="57"/>
+      <c r="D103" s="57"/>
+      <c r="E103" s="57"/>
+      <c r="F103" s="57"/>
+      <c r="G103" s="57"/>
+      <c r="H103" s="57"/>
+      <c r="I103" s="57"/>
+      <c r="J103" s="57"/>
+      <c r="K103" s="57"/>
+      <c r="L103" s="57"/>
+      <c r="M103" s="57"/>
+      <c r="N103" s="57"/>
+      <c r="O103" s="57"/>
+      <c r="P103" s="57"/>
+      <c r="Q103" s="57"/>
+      <c r="R103" s="57"/>
+      <c r="S103" s="58"/>
+      <c r="T103" s="57"/>
+      <c r="U103" s="57"/>
+      <c r="V103" s="57"/>
+      <c r="W103" s="57"/>
+      <c r="X103" s="57"/>
+      <c r="Y103" s="58"/>
+      <c r="Z103" s="52"/>
+      <c r="AA103" s="42"/>
+      <c r="AB103" s="42"/>
+      <c r="AC103" s="42"/>
+      <c r="AD103" s="42"/>
+      <c r="AE103" s="42"/>
+      <c r="AF103" s="42"/>
+      <c r="AG103" s="42"/>
+      <c r="AH103" s="43"/>
     </row>
     <row r="104" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A104" s="55">
+      <c r="A104" s="56">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="B104" s="56"/>
-      <c r="C104" s="56"/>
-      <c r="D104" s="56"/>
-      <c r="E104" s="56"/>
-      <c r="F104" s="56"/>
-      <c r="G104" s="56"/>
-      <c r="H104" s="56"/>
-      <c r="I104" s="56"/>
-      <c r="J104" s="56"/>
-      <c r="K104" s="56"/>
-      <c r="L104" s="56"/>
-      <c r="M104" s="56"/>
-      <c r="N104" s="56"/>
-      <c r="O104" s="56"/>
-      <c r="P104" s="56"/>
-      <c r="Q104" s="56"/>
-      <c r="R104" s="56"/>
-      <c r="S104" s="57"/>
-      <c r="T104" s="56"/>
-      <c r="U104" s="56"/>
-      <c r="V104" s="56"/>
-      <c r="W104" s="56"/>
-      <c r="X104" s="56"/>
-      <c r="Y104" s="57"/>
-      <c r="Z104" s="51"/>
-      <c r="AA104" s="43"/>
-      <c r="AB104" s="43"/>
-      <c r="AC104" s="43"/>
-      <c r="AD104" s="43"/>
-      <c r="AE104" s="43"/>
-      <c r="AF104" s="43"/>
-      <c r="AG104" s="43"/>
-      <c r="AH104" s="44"/>
+      <c r="B104" s="57"/>
+      <c r="C104" s="57"/>
+      <c r="D104" s="57"/>
+      <c r="E104" s="57"/>
+      <c r="F104" s="57"/>
+      <c r="G104" s="57"/>
+      <c r="H104" s="57"/>
+      <c r="I104" s="57"/>
+      <c r="J104" s="57"/>
+      <c r="K104" s="57"/>
+      <c r="L104" s="57"/>
+      <c r="M104" s="57"/>
+      <c r="N104" s="57"/>
+      <c r="O104" s="57"/>
+      <c r="P104" s="57"/>
+      <c r="Q104" s="57"/>
+      <c r="R104" s="57"/>
+      <c r="S104" s="58"/>
+      <c r="T104" s="57"/>
+      <c r="U104" s="57"/>
+      <c r="V104" s="57"/>
+      <c r="W104" s="57"/>
+      <c r="X104" s="57"/>
+      <c r="Y104" s="58"/>
+      <c r="Z104" s="52"/>
+      <c r="AA104" s="42"/>
+      <c r="AB104" s="42"/>
+      <c r="AC104" s="42"/>
+      <c r="AD104" s="42"/>
+      <c r="AE104" s="42"/>
+      <c r="AF104" s="42"/>
+      <c r="AG104" s="42"/>
+      <c r="AH104" s="43"/>
     </row>
     <row r="105" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A105" s="55">
+      <c r="A105" s="56">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="B105" s="56"/>
-      <c r="C105" s="56"/>
-      <c r="D105" s="56"/>
-      <c r="E105" s="56"/>
-      <c r="F105" s="56"/>
-      <c r="G105" s="56"/>
-      <c r="H105" s="56"/>
-      <c r="I105" s="56"/>
-      <c r="J105" s="56"/>
-      <c r="K105" s="56"/>
-      <c r="L105" s="56"/>
-      <c r="M105" s="56"/>
-      <c r="N105" s="56"/>
-      <c r="O105" s="56"/>
-      <c r="P105" s="56"/>
-      <c r="Q105" s="56"/>
-      <c r="R105" s="56"/>
-      <c r="S105" s="57"/>
-      <c r="T105" s="56"/>
-      <c r="U105" s="56"/>
-      <c r="V105" s="56"/>
-      <c r="W105" s="56"/>
-      <c r="X105" s="56"/>
-      <c r="Y105" s="57"/>
-      <c r="Z105" s="51"/>
-      <c r="AA105" s="43"/>
-      <c r="AB105" s="43"/>
-      <c r="AC105" s="43"/>
-      <c r="AD105" s="43"/>
-      <c r="AE105" s="43"/>
-      <c r="AF105" s="43"/>
-      <c r="AG105" s="43"/>
-      <c r="AH105" s="44"/>
+      <c r="B105" s="57"/>
+      <c r="C105" s="57"/>
+      <c r="D105" s="57"/>
+      <c r="E105" s="57"/>
+      <c r="F105" s="57"/>
+      <c r="G105" s="57"/>
+      <c r="H105" s="57"/>
+      <c r="I105" s="57"/>
+      <c r="J105" s="57"/>
+      <c r="K105" s="57"/>
+      <c r="L105" s="57"/>
+      <c r="M105" s="57"/>
+      <c r="N105" s="57"/>
+      <c r="O105" s="57"/>
+      <c r="P105" s="57"/>
+      <c r="Q105" s="57"/>
+      <c r="R105" s="57"/>
+      <c r="S105" s="58"/>
+      <c r="T105" s="57"/>
+      <c r="U105" s="57"/>
+      <c r="V105" s="57"/>
+      <c r="W105" s="57"/>
+      <c r="X105" s="57"/>
+      <c r="Y105" s="58"/>
+      <c r="Z105" s="52"/>
+      <c r="AA105" s="42"/>
+      <c r="AB105" s="42"/>
+      <c r="AC105" s="42"/>
+      <c r="AD105" s="42"/>
+      <c r="AE105" s="42"/>
+      <c r="AF105" s="42"/>
+      <c r="AG105" s="42"/>
+      <c r="AH105" s="43"/>
     </row>
     <row r="106" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A106" s="55">
+      <c r="A106" s="56">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="B106" s="56"/>
-      <c r="C106" s="56"/>
-      <c r="D106" s="56"/>
-      <c r="E106" s="56"/>
-      <c r="F106" s="56"/>
-      <c r="G106" s="56"/>
-      <c r="H106" s="56"/>
-      <c r="I106" s="56"/>
-      <c r="J106" s="56"/>
-      <c r="K106" s="56"/>
-      <c r="L106" s="56"/>
-      <c r="M106" s="56"/>
-      <c r="N106" s="56"/>
-      <c r="O106" s="56"/>
-      <c r="P106" s="56"/>
-      <c r="Q106" s="56"/>
-      <c r="R106" s="56"/>
-      <c r="S106" s="57"/>
-      <c r="T106" s="56"/>
-      <c r="U106" s="56"/>
-      <c r="V106" s="56"/>
-      <c r="W106" s="56"/>
-      <c r="X106" s="56"/>
-      <c r="Y106" s="57"/>
-      <c r="Z106" s="51"/>
-      <c r="AA106" s="43"/>
-      <c r="AB106" s="43"/>
-      <c r="AC106" s="43"/>
-      <c r="AD106" s="43"/>
-      <c r="AE106" s="43"/>
-      <c r="AF106" s="43"/>
-      <c r="AG106" s="43"/>
-      <c r="AH106" s="44"/>
+      <c r="B106" s="57"/>
+      <c r="C106" s="57"/>
+      <c r="D106" s="57"/>
+      <c r="E106" s="57"/>
+      <c r="F106" s="57"/>
+      <c r="G106" s="57"/>
+      <c r="H106" s="57"/>
+      <c r="I106" s="57"/>
+      <c r="J106" s="57"/>
+      <c r="K106" s="57"/>
+      <c r="L106" s="57"/>
+      <c r="M106" s="57"/>
+      <c r="N106" s="57"/>
+      <c r="O106" s="57"/>
+      <c r="P106" s="57"/>
+      <c r="Q106" s="57"/>
+      <c r="R106" s="57"/>
+      <c r="S106" s="58"/>
+      <c r="T106" s="57"/>
+      <c r="U106" s="57"/>
+      <c r="V106" s="57"/>
+      <c r="W106" s="57"/>
+      <c r="X106" s="57"/>
+      <c r="Y106" s="58"/>
+      <c r="Z106" s="52"/>
+      <c r="AA106" s="42"/>
+      <c r="AB106" s="42"/>
+      <c r="AC106" s="42"/>
+      <c r="AD106" s="42"/>
+      <c r="AE106" s="42"/>
+      <c r="AF106" s="42"/>
+      <c r="AG106" s="42"/>
+      <c r="AH106" s="43"/>
     </row>
     <row r="107" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A107" s="55">
+      <c r="A107" s="56">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="B107" s="56"/>
-      <c r="C107" s="56"/>
-      <c r="D107" s="56"/>
-      <c r="E107" s="56"/>
-      <c r="F107" s="56"/>
-      <c r="G107" s="56"/>
-      <c r="H107" s="56"/>
-      <c r="I107" s="56"/>
-      <c r="J107" s="56"/>
-      <c r="K107" s="56"/>
-      <c r="L107" s="56"/>
-      <c r="M107" s="56"/>
-      <c r="N107" s="56"/>
-      <c r="O107" s="56"/>
-      <c r="P107" s="56"/>
-      <c r="Q107" s="56"/>
-      <c r="R107" s="56"/>
-      <c r="S107" s="57"/>
-      <c r="T107" s="56"/>
-      <c r="U107" s="56"/>
-      <c r="V107" s="56"/>
-      <c r="W107" s="56"/>
-      <c r="X107" s="56"/>
-      <c r="Y107" s="57"/>
-      <c r="Z107" s="51"/>
-      <c r="AA107" s="43"/>
-      <c r="AB107" s="43"/>
-      <c r="AC107" s="43"/>
-      <c r="AD107" s="43"/>
-      <c r="AE107" s="43"/>
-      <c r="AF107" s="43"/>
-      <c r="AG107" s="43"/>
-      <c r="AH107" s="44"/>
+      <c r="B107" s="57"/>
+      <c r="C107" s="57"/>
+      <c r="D107" s="57"/>
+      <c r="E107" s="57"/>
+      <c r="F107" s="57"/>
+      <c r="G107" s="57"/>
+      <c r="H107" s="57"/>
+      <c r="I107" s="57"/>
+      <c r="J107" s="57"/>
+      <c r="K107" s="57"/>
+      <c r="L107" s="57"/>
+      <c r="M107" s="57"/>
+      <c r="N107" s="57"/>
+      <c r="O107" s="57"/>
+      <c r="P107" s="57"/>
+      <c r="Q107" s="57"/>
+      <c r="R107" s="57"/>
+      <c r="S107" s="58"/>
+      <c r="T107" s="57"/>
+      <c r="U107" s="57"/>
+      <c r="V107" s="57"/>
+      <c r="W107" s="57"/>
+      <c r="X107" s="57"/>
+      <c r="Y107" s="58"/>
+      <c r="Z107" s="52"/>
+      <c r="AA107" s="42"/>
+      <c r="AB107" s="42"/>
+      <c r="AC107" s="42"/>
+      <c r="AD107" s="42"/>
+      <c r="AE107" s="42"/>
+      <c r="AF107" s="42"/>
+      <c r="AG107" s="42"/>
+      <c r="AH107" s="43"/>
     </row>
     <row r="108" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A108" s="55">
+      <c r="A108" s="56">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="B108" s="56"/>
-      <c r="C108" s="56"/>
-      <c r="D108" s="56"/>
-      <c r="E108" s="56"/>
-      <c r="F108" s="56"/>
-      <c r="G108" s="56"/>
-      <c r="H108" s="56"/>
-      <c r="I108" s="56"/>
-      <c r="J108" s="56"/>
-      <c r="K108" s="56"/>
-      <c r="L108" s="56"/>
-      <c r="M108" s="56"/>
-      <c r="N108" s="56"/>
-      <c r="O108" s="56"/>
-      <c r="P108" s="56"/>
-      <c r="Q108" s="56"/>
-      <c r="R108" s="56"/>
-      <c r="S108" s="57"/>
-      <c r="T108" s="56"/>
-      <c r="U108" s="56"/>
-      <c r="V108" s="56"/>
-      <c r="W108" s="56"/>
-      <c r="X108" s="56"/>
-      <c r="Y108" s="57"/>
-      <c r="Z108" s="51"/>
-      <c r="AA108" s="43"/>
-      <c r="AB108" s="43"/>
-      <c r="AC108" s="43"/>
-      <c r="AD108" s="43"/>
-      <c r="AE108" s="43"/>
-      <c r="AF108" s="43"/>
-      <c r="AG108" s="43"/>
-      <c r="AH108" s="44"/>
+      <c r="B108" s="57"/>
+      <c r="C108" s="57"/>
+      <c r="D108" s="57"/>
+      <c r="E108" s="57"/>
+      <c r="F108" s="57"/>
+      <c r="G108" s="57"/>
+      <c r="H108" s="57"/>
+      <c r="I108" s="57"/>
+      <c r="J108" s="57"/>
+      <c r="K108" s="57"/>
+      <c r="L108" s="57"/>
+      <c r="M108" s="57"/>
+      <c r="N108" s="57"/>
+      <c r="O108" s="57"/>
+      <c r="P108" s="57"/>
+      <c r="Q108" s="57"/>
+      <c r="R108" s="57"/>
+      <c r="S108" s="58"/>
+      <c r="T108" s="57"/>
+      <c r="U108" s="57"/>
+      <c r="V108" s="57"/>
+      <c r="W108" s="57"/>
+      <c r="X108" s="57"/>
+      <c r="Y108" s="58"/>
+      <c r="Z108" s="52"/>
+      <c r="AA108" s="42"/>
+      <c r="AB108" s="42"/>
+      <c r="AC108" s="42"/>
+      <c r="AD108" s="42"/>
+      <c r="AE108" s="42"/>
+      <c r="AF108" s="42"/>
+      <c r="AG108" s="42"/>
+      <c r="AH108" s="43"/>
     </row>
     <row r="109" spans="1:34" ht="15.75" customHeight="1"/>
     <row r="110" spans="1:34" ht="15.75" customHeight="1"/>
